--- a/outputs/marine_equipment/План_загрузки_контейнера.xlsx
+++ b/outputs/marine_equipment/План_загрузки_контейнера.xlsx
@@ -784,7 +784,7 @@
         <v>4633</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>33</v>
@@ -878,23 +878,23 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>Брашпили, лебедки, трал, подруливающие</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="C16" s="18" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>14</v>
+        <v>216</v>
       </c>
       <c r="E16" s="20" t="n">
-        <v>20.2</v>
+        <v>20.6</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>522500</v>
+        <v>17581000</v>
       </c>
     </row>
     <row r="17">
@@ -905,23 +905,23 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Брашпили, лебедки, трал, подруливающие</t>
         </is>
       </c>
       <c r="C17" s="18" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>216</v>
+        <v>14</v>
       </c>
       <c r="E17" s="20" t="n">
-        <v>19.1</v>
+        <v>20.2</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G17" s="21" t="n">
-        <v>17581000</v>
+        <v>522500</v>
       </c>
     </row>
     <row r="18">
@@ -1019,7 +1019,7 @@
         <v>545</v>
       </c>
       <c r="E21" s="23" t="n">
-        <v>63.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="F21" s="22" t="n">
         <v>121</v>
@@ -3462,29 +3462,29 @@
       </c>
       <c r="C58" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="D58" s="33" t="inlineStr">
         <is>
-          <t>Сетка на фильтр Ду100 (медь) на кингстон РС-300</t>
+          <t>Диски тормозные 225мм</t>
         </is>
       </c>
       <c r="E58" s="34" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F58" s="35" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="G58" s="35" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H58" s="36" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="I58" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -3499,29 +3499,29 @@
       </c>
       <c r="C59" s="34" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D59" s="33" t="inlineStr">
         <is>
-          <t>Диски тормозные 225мм</t>
+          <t>Клапан невозвратно-приемный фланцевый Ду 50 Ру1 (522-35.4043-01)</t>
         </is>
       </c>
       <c r="E59" s="34" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F59" s="35" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G59" s="35" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H59" s="36" t="n">
-        <v>0.11</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="I59" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -3536,29 +3536,29 @@
       </c>
       <c r="C60" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D60" s="33" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 50 Ру1 (522-35.4043-01)</t>
+          <t>Головка блока цилиндра 3D6</t>
         </is>
       </c>
       <c r="E60" s="34" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F60" s="35" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="G60" s="35" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H60" s="36" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.02</v>
       </c>
       <c r="I60" s="34" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -3573,29 +3573,29 @@
       </c>
       <c r="C61" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D61" s="33" t="inlineStr">
         <is>
-          <t>Головка блока цилиндра 3D6</t>
+          <t>Клапан фланцевый угловой Ду25</t>
         </is>
       </c>
       <c r="E61" s="34" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F61" s="35" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G61" s="35" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H61" s="36" t="n">
-        <v>0.02</v>
+        <v>0.045</v>
       </c>
       <c r="I61" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -3610,29 +3610,29 @@
       </c>
       <c r="C62" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
         </is>
       </c>
       <c r="D62" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду25</t>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду125 (без поплавка) (541-03.220)</t>
         </is>
       </c>
       <c r="E62" s="34" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F62" s="35" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G62" s="35" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H62" s="36" t="n">
-        <v>0.045</v>
+        <v>0.06</v>
       </c>
       <c r="I62" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -3652,24 +3652,24 @@
       </c>
       <c r="D63" s="33" t="inlineStr">
         <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду125 (без поплавка) (541-03.220)</t>
+          <t>Фланец свободный Ду80</t>
         </is>
       </c>
       <c r="E63" s="34" t="n">
+        <v>12</v>
+      </c>
+      <c r="F63" s="35" t="n">
         <v>6</v>
-      </c>
-      <c r="F63" s="35" t="n">
-        <v>12</v>
       </c>
       <c r="G63" s="35" t="n">
         <v>72</v>
       </c>
       <c r="H63" s="36" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="I63" s="34" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -3684,29 +3684,29 @@
       </c>
       <c r="C64" s="34" t="inlineStr">
         <is>
-          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D64" s="33" t="inlineStr">
         <is>
-          <t>Фланец свободный Ду80</t>
+          <t>Толкатель (пята) 602-061-108</t>
         </is>
       </c>
       <c r="E64" s="34" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="F64" s="35" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="G64" s="35" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H64" s="36" t="n">
-        <v>0.12</v>
+        <v>0.47</v>
       </c>
       <c r="I64" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -3721,29 +3721,29 @@
       </c>
       <c r="C65" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D65" s="33" t="inlineStr">
         <is>
-          <t>Толкатель (пята) 602-061-108</t>
+          <t>Клапан фланцевый проходной титановые Ду50Ру10</t>
         </is>
       </c>
       <c r="E65" s="34" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="F65" s="35" t="n">
-        <v>1.5</v>
+        <v>14</v>
       </c>
       <c r="G65" s="35" t="n">
         <v>70</v>
       </c>
       <c r="H65" s="36" t="n">
-        <v>0.47</v>
+        <v>0.06</v>
       </c>
       <c r="I65" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -3763,14 +3763,14 @@
       </c>
       <c r="D66" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной титановые Ду50Ру10</t>
+          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
         </is>
       </c>
       <c r="E66" s="34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F66" s="35" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="G66" s="35" t="n">
         <v>70</v>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="I66" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -3800,14 +3800,14 @@
       </c>
       <c r="D67" s="33" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
+          <t>Клапан фланцевый проходной Ду50 Ру25</t>
         </is>
       </c>
       <c r="E67" s="34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F67" s="35" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="G67" s="35" t="n">
         <v>70</v>
@@ -3837,20 +3837,20 @@
       </c>
       <c r="D68" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду50 Ру25</t>
+          <t>Клапан быстрозапор. фланц. проход. с тросиков. приводом Ду40Ру6,3</t>
         </is>
       </c>
       <c r="E68" s="34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F68" s="35" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G68" s="35" t="n">
         <v>70</v>
       </c>
       <c r="H68" s="36" t="n">
-        <v>0.06</v>
+        <v>0.056</v>
       </c>
       <c r="I68" s="34" t="inlineStr">
         <is>
@@ -3874,20 +3874,20 @@
       </c>
       <c r="D69" s="33" t="inlineStr">
         <is>
-          <t>Клапан быстрозапор. фланц. проход. с тросиков. приводом Ду40Ру6,3</t>
+          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50</t>
         </is>
       </c>
       <c r="E69" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="F69" s="35" t="n">
         <v>7</v>
-      </c>
-      <c r="F69" s="35" t="n">
-        <v>10</v>
       </c>
       <c r="G69" s="35" t="n">
         <v>70</v>
       </c>
       <c r="H69" s="36" t="n">
-        <v>0.056</v>
+        <v>0.12</v>
       </c>
       <c r="I69" s="34" t="inlineStr">
         <is>
@@ -3911,24 +3911,24 @@
       </c>
       <c r="D70" s="33" t="inlineStr">
         <is>
-          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50</t>
+          <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду70 Ру6,3</t>
         </is>
       </c>
       <c r="E70" s="34" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F70" s="35" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="G70" s="35" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H70" s="36" t="n">
-        <v>0.12</v>
+        <v>0.066</v>
       </c>
       <c r="I70" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -3943,29 +3943,29 @@
       </c>
       <c r="C71" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D71" s="33" t="inlineStr">
         <is>
-          <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду70 Ру6,3</t>
+          <t>Сухари</t>
         </is>
       </c>
       <c r="E71" s="34" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="F71" s="35" t="n">
-        <v>23</v>
+        <v>1.5</v>
       </c>
       <c r="G71" s="35" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H71" s="36" t="n">
-        <v>0.066</v>
+        <v>0.44</v>
       </c>
       <c r="I71" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -3980,29 +3980,29 @@
       </c>
       <c r="C72" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Насосы</t>
         </is>
       </c>
       <c r="D72" s="33" t="inlineStr">
         <is>
-          <t>Сухари</t>
+          <t>Колесо раб.Насос 1ЭЦНУ 16/40</t>
         </is>
       </c>
       <c r="E72" s="34" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="F72" s="35" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="G72" s="35" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H72" s="36" t="n">
-        <v>0.44</v>
+        <v>0.08</v>
       </c>
       <c r="I72" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -4017,25 +4017,25 @@
       </c>
       <c r="C73" s="34" t="inlineStr">
         <is>
-          <t>Насосы</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D73" s="33" t="inlineStr">
         <is>
-          <t>Колесо раб.Насос 1ЭЦНУ 16/40</t>
+          <t>Клапан фланцевый угловой Ду65 Ру10</t>
         </is>
       </c>
       <c r="E73" s="34" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F73" s="35" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G73" s="35" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H73" s="36" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="I73" s="34" t="inlineStr">
         <is>
@@ -4054,25 +4054,25 @@
       </c>
       <c r="C74" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Насосы</t>
         </is>
       </c>
       <c r="D74" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду65 Ру10</t>
+          <t>Поплавок НЦВС 40/20</t>
         </is>
       </c>
       <c r="E74" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="F74" s="35" t="n">
         <v>3</v>
-      </c>
-      <c r="F74" s="35" t="n">
-        <v>20</v>
       </c>
       <c r="G74" s="35" t="n">
         <v>60</v>
       </c>
       <c r="H74" s="36" t="n">
-        <v>0.06</v>
+        <v>0.2</v>
       </c>
       <c r="I74" s="34" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="D75" s="33" t="inlineStr">
         <is>
-          <t>Поплавок НЦВС 40/20</t>
+          <t>РТИ НЦКГ 4/40</t>
         </is>
       </c>
       <c r="E75" s="34" t="n">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="I75" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -4128,25 +4128,25 @@
       </c>
       <c r="C76" s="34" t="inlineStr">
         <is>
-          <t>Насосы</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D76" s="33" t="inlineStr">
         <is>
-          <t>РТИ НЦКГ 4/40</t>
+          <t>Направляющий клапан (маленький)</t>
         </is>
       </c>
       <c r="E76" s="34" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F76" s="35" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G76" s="35" t="n">
         <v>60</v>
       </c>
       <c r="H76" s="36" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I76" s="34" t="inlineStr">
         <is>
@@ -4165,29 +4165,29 @@
       </c>
       <c r="C77" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D77" s="33" t="inlineStr">
         <is>
-          <t>Направляющий клапан (маленький)</t>
+          <t>Задвижка клинкетная Ду80 ( в разборе)</t>
         </is>
       </c>
       <c r="E77" s="34" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="F77" s="35" t="n">
-        <v>1.5</v>
+        <v>28</v>
       </c>
       <c r="G77" s="35" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H77" s="36" t="n">
-        <v>0.4</v>
+        <v>0.06</v>
       </c>
       <c r="I77" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="D78" s="33" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду80 ( в разборе)</t>
+          <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду80 Ру6,3</t>
         </is>
       </c>
       <c r="E78" s="34" t="n">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="I78" s="34" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -4239,29 +4239,29 @@
       </c>
       <c r="C79" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="D79" s="33" t="inlineStr">
         <is>
-          <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду80 Ру6,3</t>
+          <t>Диски тормозные ТДП-6А Ф400</t>
         </is>
       </c>
       <c r="E79" s="34" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F79" s="35" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="G79" s="35" t="n">
         <v>56</v>
       </c>
       <c r="H79" s="36" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I79" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -4276,29 +4276,29 @@
       </c>
       <c r="C80" s="34" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D80" s="33" t="inlineStr">
         <is>
-          <t>Диски тормозные ТДП-6А Ф400</t>
+          <t>Клапан штуцерный угловой Ду32 Ру160</t>
         </is>
       </c>
       <c r="E80" s="34" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F80" s="35" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="G80" s="35" t="n">
         <v>56</v>
       </c>
       <c r="H80" s="36" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I80" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -4313,29 +4313,29 @@
       </c>
       <c r="C81" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D81" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32 Ру160</t>
+          <t>Пружина нагнетательного клапана ТНВД</t>
         </is>
       </c>
       <c r="E81" s="34" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F81" s="35" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="G81" s="35" t="n">
         <v>56</v>
       </c>
       <c r="H81" s="36" t="n">
-        <v>0.08</v>
+        <v>0.018</v>
       </c>
       <c r="I81" s="34" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="D82" s="33" t="inlineStr">
         <is>
-          <t>Пружина нагнетательного клапана ТНВД</t>
+          <t>Кольцо уплотнительное под плунжер</t>
         </is>
       </c>
       <c r="E82" s="34" t="n">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="D83" s="33" t="inlineStr">
         <is>
-          <t>Кольцо уплотнительное под плунжер</t>
+          <t>Пружина нагнетательного клапана VD26/20</t>
         </is>
       </c>
       <c r="E83" s="34" t="n">
@@ -4424,29 +4424,29 @@
       </c>
       <c r="C84" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D84" s="33" t="inlineStr">
         <is>
-          <t>Пружина нагнетательного клапана VD26/20</t>
+          <t>Кран штуцерный спусковой самозапорный проходной Ду20 Ру10</t>
         </is>
       </c>
       <c r="E84" s="34" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F84" s="35" t="n">
         <v>1.5</v>
       </c>
       <c r="G84" s="35" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H84" s="36" t="n">
-        <v>0.018</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="I84" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -4461,29 +4461,29 @@
       </c>
       <c r="C85" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
         </is>
       </c>
       <c r="D85" s="33" t="inlineStr">
         <is>
-          <t>Кран штуцерный спусковой самозапорный проходной Ду20 Ру10</t>
+          <t>Гайки алюминевые б/у</t>
         </is>
       </c>
       <c r="E85" s="34" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F85" s="35" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G85" s="35" t="n">
         <v>54</v>
       </c>
       <c r="H85" s="36" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="I85" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -4498,29 +4498,29 @@
       </c>
       <c r="C86" s="34" t="inlineStr">
         <is>
-          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D86" s="33" t="inlineStr">
         <is>
-          <t>Гайки алюминевые б/у</t>
+          <t>Направляющий клапан (большой)</t>
         </is>
       </c>
       <c r="E86" s="34" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F86" s="35" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G86" s="35" t="n">
         <v>54</v>
       </c>
       <c r="H86" s="36" t="n">
-        <v>0.27</v>
+        <v>0.36</v>
       </c>
       <c r="I86" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -4535,29 +4535,29 @@
       </c>
       <c r="C87" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D87" s="33" t="inlineStr">
         <is>
-          <t>Направляющий клапан (большой)</t>
+          <t>Клапан штуцерный проходной Ду 10</t>
         </is>
       </c>
       <c r="E87" s="34" t="n">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="F87" s="35" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="G87" s="35" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H87" s="36" t="n">
-        <v>0.36</v>
+        <v>0.083</v>
       </c>
       <c r="I87" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -4577,24 +4577,24 @@
       </c>
       <c r="D88" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10</t>
+          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
         </is>
       </c>
       <c r="E88" s="34" t="n">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="F88" s="35" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="G88" s="35" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H88" s="36" t="n">
-        <v>0.083</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I88" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -4609,29 +4609,29 @@
       </c>
       <c r="C89" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D89" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
+          <t>Винт толкателя</t>
         </is>
       </c>
       <c r="E89" s="34" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F89" s="35" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="G89" s="35" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H89" s="36" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.016</v>
       </c>
       <c r="I89" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -4646,29 +4646,29 @@
       </c>
       <c r="C90" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D90" s="33" t="inlineStr">
         <is>
-          <t>Винт толкателя</t>
+          <t>Клапан фланцевый проходной Ду70 Ру10</t>
         </is>
       </c>
       <c r="E90" s="34" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F90" s="35" t="n">
-        <v>1.5</v>
+        <v>23</v>
       </c>
       <c r="G90" s="35" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H90" s="36" t="n">
-        <v>0.016</v>
+        <v>0.044</v>
       </c>
       <c r="I90" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -4688,24 +4688,24 @@
       </c>
       <c r="D91" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду70 Ру10</t>
+          <t>Клапан редукционный штуц.проход.односедельный Ду20Ру400 у входа</t>
         </is>
       </c>
       <c r="E91" s="34" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F91" s="35" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="G91" s="35" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H91" s="36" t="n">
-        <v>0.044</v>
+        <v>0.018</v>
       </c>
       <c r="I91" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -4725,24 +4725,24 @@
       </c>
       <c r="D92" s="33" t="inlineStr">
         <is>
-          <t>Клапан редукционный штуц.проход.односедельный Ду20Ру400 у входа</t>
+          <t>Клапан штущерный проходной Ду15</t>
         </is>
       </c>
       <c r="E92" s="34" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="F92" s="35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G92" s="35" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H92" s="36" t="n">
-        <v>0.018</v>
+        <v>0.066</v>
       </c>
       <c r="I92" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -4757,29 +4757,29 @@
       </c>
       <c r="C93" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D93" s="33" t="inlineStr">
         <is>
-          <t>Клапан штущерный проходной Ду15</t>
+          <t>Болт шатунный(мотылев)</t>
         </is>
       </c>
       <c r="E93" s="34" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F93" s="35" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G93" s="35" t="n">
         <v>44</v>
       </c>
       <c r="H93" s="36" t="n">
-        <v>0.066</v>
+        <v>0.015</v>
       </c>
       <c r="I93" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -4794,29 +4794,29 @@
       </c>
       <c r="C94" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D94" s="33" t="inlineStr">
         <is>
-          <t>Болт шатунный(мотылев)</t>
+          <t>Клапан проходной фланцевый Ду32 - БРАК</t>
         </is>
       </c>
       <c r="E94" s="34" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="F94" s="35" t="n">
-        <v>1.5</v>
+        <v>7</v>
       </c>
       <c r="G94" s="35" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H94" s="36" t="n">
-        <v>0.015</v>
+        <v>0.03</v>
       </c>
       <c r="I94" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="D95" s="33" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый Ду32 - БРАК</t>
+          <t>Клапан фланцевый проходной ДУ32 Ру25</t>
         </is>
       </c>
       <c r="E95" s="34" t="n">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="I95" s="34" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -4873,24 +4873,24 @@
       </c>
       <c r="D96" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной ДУ32 Ру25</t>
+          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
         </is>
       </c>
       <c r="E96" s="34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F96" s="35" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G96" s="35" t="n">
         <v>42</v>
       </c>
       <c r="H96" s="36" t="n">
-        <v>0.03</v>
+        <v>0.036</v>
       </c>
       <c r="I96" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -4910,24 +4910,24 @@
       </c>
       <c r="D97" s="33" t="inlineStr">
         <is>
-          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
+          <t>Электропривод к задвижке</t>
         </is>
       </c>
       <c r="E97" s="34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F97" s="35" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="G97" s="35" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H97" s="36" t="n">
-        <v>0.036</v>
+        <v>0.01</v>
       </c>
       <c r="I97" s="34" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Гараж 2</t>
         </is>
       </c>
     </row>
@@ -4947,24 +4947,24 @@
       </c>
       <c r="D98" s="33" t="inlineStr">
         <is>
-          <t>Электропривод к задвижке</t>
+          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
         </is>
       </c>
       <c r="E98" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="35" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G98" s="35" t="n">
         <v>40</v>
       </c>
       <c r="H98" s="36" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="I98" s="34" t="inlineStr">
         <is>
-          <t>Гараж 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -4984,24 +4984,24 @@
       </c>
       <c r="D99" s="33" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
+          <t>Клапан фланцевый проходной титановые Ду100Ру10</t>
         </is>
       </c>
       <c r="E99" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F99" s="35" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G99" s="35" t="n">
         <v>40</v>
       </c>
       <c r="H99" s="36" t="n">
-        <v>0.04</v>
+        <v>0.045</v>
       </c>
       <c r="I99" s="34" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -5021,20 +5021,20 @@
       </c>
       <c r="D100" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной титановые Ду100Ру10</t>
+          <t>Клапан пусковой Ду32Ру125</t>
         </is>
       </c>
       <c r="E100" s="34" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F100" s="35" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G100" s="35" t="n">
         <v>40</v>
       </c>
       <c r="H100" s="36" t="n">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="I100" s="34" t="inlineStr">
         <is>
@@ -5058,24 +5058,24 @@
       </c>
       <c r="D101" s="33" t="inlineStr">
         <is>
-          <t>Клапан пусковой Ду32Ру125</t>
+          <t>Клапан проходной фланцевый сталь</t>
         </is>
       </c>
       <c r="E101" s="34" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F101" s="35" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G101" s="35" t="n">
         <v>40</v>
       </c>
       <c r="H101" s="36" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="I101" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -5095,20 +5095,20 @@
       </c>
       <c r="D102" s="33" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый сталь</t>
+          <t>Фильтр забортной воды Ду 100</t>
         </is>
       </c>
       <c r="E102" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F102" s="35" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G102" s="35" t="n">
         <v>40</v>
       </c>
       <c r="H102" s="36" t="n">
-        <v>0.02</v>
+        <v>0.045</v>
       </c>
       <c r="I102" s="34" t="inlineStr">
         <is>
@@ -7574,24 +7574,24 @@
       </c>
       <c r="D169" s="33" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду60</t>
+          <t>Сетка на фильтр Ду100 или Ду80</t>
         </is>
       </c>
       <c r="E169" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F169" s="35" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G169" s="35" t="n">
         <v>16</v>
       </c>
       <c r="H169" s="36" t="n">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="I169" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -7606,12 +7606,12 @@
       </c>
       <c r="C170" s="34" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D170" s="33" t="inlineStr">
         <is>
-          <t>Диски тормозные 185мм</t>
+          <t>Сетка на фильтр Ду100 (медь) на кингстон РС-300</t>
         </is>
       </c>
       <c r="E170" s="34" t="n">
@@ -7624,11 +7624,11 @@
         <v>16</v>
       </c>
       <c r="H170" s="36" t="n">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="I170" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -7648,24 +7648,24 @@
       </c>
       <c r="D171" s="33" t="inlineStr">
         <is>
-          <t>Клапан Ду20/10</t>
+          <t>Задвижка клинкетная Ду60</t>
         </is>
       </c>
       <c r="E171" s="34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F171" s="35" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G171" s="35" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H171" s="36" t="n">
-        <v>0.006</v>
+        <v>0.02</v>
       </c>
       <c r="I171" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -7680,25 +7680,25 @@
       </c>
       <c r="C172" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="D172" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду25</t>
+          <t>Диски тормозные 185мм</t>
         </is>
       </c>
       <c r="E172" s="34" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F172" s="35" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G172" s="35" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H172" s="36" t="n">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
       <c r="I172" s="34" t="inlineStr">
         <is>
@@ -7717,29 +7717,29 @@
       </c>
       <c r="C173" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D173" s="33" t="inlineStr">
         <is>
-          <t>Клапан выхлопной</t>
+          <t>Клапан Ду20/10</t>
         </is>
       </c>
       <c r="E173" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F173" s="35" t="n">
         <v>5</v>
-      </c>
-      <c r="F173" s="35" t="n">
-        <v>3</v>
       </c>
       <c r="G173" s="35" t="n">
         <v>15</v>
       </c>
       <c r="H173" s="36" t="n">
-        <v>0.05</v>
+        <v>0.006</v>
       </c>
       <c r="I173" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -7759,24 +7759,24 @@
       </c>
       <c r="D174" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15 Ру100</t>
+          <t>Клапан штуцерный угловой Ду25</t>
         </is>
       </c>
       <c r="E174" s="34" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F174" s="35" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="G174" s="35" t="n">
         <v>15</v>
       </c>
       <c r="H174" s="36" t="n">
-        <v>0.022</v>
+        <v>0.018</v>
       </c>
       <c r="I174" s="34" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -7791,29 +7791,29 @@
       </c>
       <c r="C175" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D175" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной невозвратный Ду 50 РУ 25 (522-01.164)</t>
+          <t>Клапан выхлопной</t>
         </is>
       </c>
       <c r="E175" s="34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F175" s="35" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G175" s="35" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H175" s="36" t="n">
-        <v>0.012</v>
+        <v>0.05</v>
       </c>
       <c r="I175" s="34" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -7833,24 +7833,24 @@
       </c>
       <c r="D176" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
+          <t>Клапан штуцерный угловой Ду15 Ру100</t>
         </is>
       </c>
       <c r="E176" s="34" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F176" s="35" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G176" s="35" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H176" s="36" t="n">
-        <v>0.012</v>
+        <v>0.022</v>
       </c>
       <c r="I176" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -7870,24 +7870,24 @@
       </c>
       <c r="D177" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
+          <t>Фильтр забортной воды Ду 50</t>
         </is>
       </c>
       <c r="E177" s="34" t="n">
         <v>1</v>
       </c>
       <c r="F177" s="35" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G177" s="35" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H177" s="36" t="n">
         <v>0.012</v>
       </c>
       <c r="I177" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -7907,24 +7907,24 @@
       </c>
       <c r="D178" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру16</t>
+          <t>Клапан фланцевый проходной невозвратный Ду 50 РУ 25 (522-01.164)</t>
         </is>
       </c>
       <c r="E178" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F178" s="35" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G178" s="35" t="n">
         <v>14</v>
       </c>
       <c r="H178" s="36" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="I178" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -7944,24 +7944,24 @@
       </c>
       <c r="D179" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной ДУ32 Ру25</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
         </is>
       </c>
       <c r="E179" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F179" s="35" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G179" s="35" t="n">
         <v>14</v>
       </c>
       <c r="H179" s="36" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="I179" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -7976,29 +7976,29 @@
       </c>
       <c r="C180" s="34" t="inlineStr">
         <is>
-          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D180" s="33" t="inlineStr">
         <is>
-          <t>Гайка Богданова муфтовая Ду65Ру10</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
         </is>
       </c>
       <c r="E180" s="34" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F180" s="35" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G180" s="35" t="n">
         <v>14</v>
       </c>
       <c r="H180" s="36" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.012</v>
       </c>
       <c r="I180" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -8013,29 +8013,29 @@
       </c>
       <c r="C181" s="34" t="inlineStr">
         <is>
-          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D181" s="33" t="inlineStr">
         <is>
-          <t>Гайка Шторца муфтовая Ду80Ру10</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру16</t>
         </is>
       </c>
       <c r="E181" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F181" s="35" t="n">
         <v>7</v>
-      </c>
-      <c r="F181" s="35" t="n">
-        <v>2</v>
       </c>
       <c r="G181" s="35" t="n">
         <v>14</v>
       </c>
       <c r="H181" s="36" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="I181" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -8055,24 +8055,24 @@
       </c>
       <c r="D182" s="33" t="inlineStr">
         <is>
-          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
+          <t>Клапан фланцевый проходной ДУ32 Ру25</t>
         </is>
       </c>
       <c r="E182" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F182" s="35" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G182" s="35" t="n">
         <v>14</v>
       </c>
       <c r="H182" s="36" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="I182" s="34" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -8087,29 +8087,29 @@
       </c>
       <c r="C183" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
         </is>
       </c>
       <c r="D183" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Гайка Богданова муфтовая Ду65Ру10</t>
         </is>
       </c>
       <c r="E183" s="34" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F183" s="35" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G183" s="35" t="n">
         <v>14</v>
       </c>
       <c r="H183" s="36" t="n">
-        <v>0.018</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I183" s="34" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -8129,24 +8129,24 @@
       </c>
       <c r="D184" s="33" t="inlineStr">
         <is>
-          <t>Грибки Ду125 б-у</t>
+          <t>Гайка Шторца муфтовая Ду80Ру10</t>
         </is>
       </c>
       <c r="E184" s="34" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F184" s="35" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G184" s="35" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H184" s="36" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I184" s="34" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -8166,24 +8166,24 @@
       </c>
       <c r="D185" s="33" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду 50, без клиньев</t>
+          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
         </is>
       </c>
       <c r="E185" s="34" t="n">
         <v>1</v>
       </c>
       <c r="F185" s="35" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G185" s="35" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H185" s="36" t="n">
         <v>0.012</v>
       </c>
       <c r="I185" s="34" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -8203,24 +8203,24 @@
       </c>
       <c r="D186" s="33" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая вертикальная Ду50Ру63</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
       <c r="E186" s="34" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F186" s="35" t="n">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="G186" s="35" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H186" s="36" t="n">
-        <v>0.012</v>
+        <v>0.018</v>
       </c>
       <c r="I186" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -8235,12 +8235,12 @@
       </c>
       <c r="C187" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
         </is>
       </c>
       <c r="D187" s="33" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая горизонтальная Ду50</t>
+          <t>Грибки Ду125 б-у</t>
         </is>
       </c>
       <c r="E187" s="34" t="n">
@@ -8253,11 +8253,11 @@
         <v>12</v>
       </c>
       <c r="H187" s="36" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="I187" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -8272,29 +8272,29 @@
       </c>
       <c r="C188" s="34" t="inlineStr">
         <is>
-          <t>Насосы</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D188" s="33" t="inlineStr">
         <is>
-          <t>РТИ НЦВ 100/30</t>
+          <t>Задвижка клинкетная Ду 50, без клиньев</t>
         </is>
       </c>
       <c r="E188" s="34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F188" s="35" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G188" s="35" t="n">
         <v>12</v>
       </c>
       <c r="H188" s="36" t="n">
-        <v>0.04</v>
+        <v>0.012</v>
       </c>
       <c r="I188" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -8309,29 +8309,29 @@
       </c>
       <c r="C189" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D189" s="33" t="inlineStr">
         <is>
-          <t>Палец поршня VD26/20</t>
+          <t>Захлопка фланцевая вертикальная Ду50Ру63</t>
         </is>
       </c>
       <c r="E189" s="34" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F189" s="35" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="G189" s="35" t="n">
         <v>12</v>
       </c>
       <c r="H189" s="36" t="n">
-        <v>0.08</v>
+        <v>0.012</v>
       </c>
       <c r="I189" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -8346,29 +8346,29 @@
       </c>
       <c r="C190" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D190" s="33" t="inlineStr">
         <is>
-          <t>Фланец привода VD26/20</t>
+          <t>Захлопка фланцевая горизонтальная Ду50</t>
         </is>
       </c>
       <c r="E190" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F190" s="35" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G190" s="35" t="n">
         <v>12</v>
       </c>
       <c r="H190" s="36" t="n">
-        <v>0.02</v>
+        <v>0.012</v>
       </c>
       <c r="I190" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -8383,29 +8383,29 @@
       </c>
       <c r="C191" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Насосы</t>
         </is>
       </c>
       <c r="D191" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру40</t>
+          <t>РТИ НЦВ 100/30</t>
         </is>
       </c>
       <c r="E191" s="34" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F191" s="35" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="G191" s="35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H191" s="36" t="n">
-        <v>0.018</v>
+        <v>0.04</v>
       </c>
       <c r="I191" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -8420,29 +8420,29 @@
       </c>
       <c r="C192" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D192" s="33" t="inlineStr">
         <is>
-          <t>Кран трехходовой штуцерный Ду20 Ру16</t>
+          <t>Палец поршня VD26/20</t>
         </is>
       </c>
       <c r="E192" s="34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F192" s="35" t="n">
         <v>1.5</v>
       </c>
       <c r="G192" s="35" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H192" s="36" t="n">
-        <v>0.014</v>
+        <v>0.08</v>
       </c>
       <c r="I192" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -8457,29 +8457,29 @@
       </c>
       <c r="C193" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D193" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Фланец привода VD26/20</t>
         </is>
       </c>
       <c r="E193" s="34" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F193" s="35" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="G193" s="35" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H193" s="36" t="n">
-        <v>0.014</v>
+        <v>0.02</v>
       </c>
       <c r="I193" s="34" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -8499,24 +8499,24 @@
       </c>
       <c r="D194" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 32 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру40</t>
         </is>
       </c>
       <c r="E194" s="34" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F194" s="35" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="G194" s="35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H194" s="36" t="n">
-        <v>0.015</v>
+        <v>0.018</v>
       </c>
       <c r="I194" s="34" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -8531,12 +8531,12 @@
       </c>
       <c r="C195" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D195" s="33" t="inlineStr">
         <is>
-          <t>Распылитель 10*0,6*140</t>
+          <t>Кран трехходовой штуцерный Ду20 Ру16</t>
         </is>
       </c>
       <c r="E195" s="34" t="n">
@@ -8549,11 +8549,11 @@
         <v>10</v>
       </c>
       <c r="H195" s="36" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.014</v>
       </c>
       <c r="I195" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -8568,12 +8568,12 @@
       </c>
       <c r="C196" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D196" s="33" t="inlineStr">
         <is>
-          <t>Седло VD26/20</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
       <c r="E196" s="34" t="n">
@@ -8586,11 +8586,11 @@
         <v>10</v>
       </c>
       <c r="H196" s="36" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.014</v>
       </c>
       <c r="I196" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -8605,29 +8605,29 @@
       </c>
       <c r="C197" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D197" s="33" t="inlineStr">
         <is>
-          <t>Кольцо маслосъемное без пружины VD26/20</t>
+          <t>Клапан штуцерный проходной Ду 32 Ру 40</t>
         </is>
       </c>
       <c r="E197" s="34" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F197" s="35" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="G197" s="35" t="n">
         <v>10</v>
       </c>
       <c r="H197" s="36" t="n">
-        <v>0.004</v>
+        <v>0.015</v>
       </c>
       <c r="I197" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -8642,29 +8642,29 @@
       </c>
       <c r="C198" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D198" s="33" t="inlineStr">
         <is>
-          <t>Клапан фреоновый саленоидный</t>
+          <t>Распылитель 10*0,6*140</t>
         </is>
       </c>
       <c r="E198" s="34" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F198" s="35" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="G198" s="35" t="n">
         <v>10</v>
       </c>
       <c r="H198" s="36" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I198" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -8679,29 +8679,29 @@
       </c>
       <c r="C199" s="34" t="inlineStr">
         <is>
-          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D199" s="33" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду10Ру100</t>
+          <t>Седло VD26/20</t>
         </is>
       </c>
       <c r="E199" s="34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F199" s="35" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G199" s="35" t="n">
         <v>10</v>
       </c>
       <c r="H199" s="36" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I199" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -8716,29 +8716,29 @@
       </c>
       <c r="C200" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D200" s="33" t="inlineStr">
         <is>
-          <t>Сетка на фильтр Ду100 или Ду80</t>
+          <t>Кольцо маслосъемное без пружины VD26/20</t>
         </is>
       </c>
       <c r="E200" s="34" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F200" s="35" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="G200" s="35" t="n">
         <v>10</v>
       </c>
       <c r="H200" s="36" t="n">
-        <v>0.09</v>
+        <v>0.004</v>
       </c>
       <c r="I200" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -8758,24 +8758,24 @@
       </c>
       <c r="D201" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду40 Ру10</t>
+          <t>Клапан фреоновый саленоидный</t>
         </is>
       </c>
       <c r="E201" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F201" s="35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G201" s="35" t="n">
         <v>10</v>
       </c>
       <c r="H201" s="36" t="n">
-        <v>0.008</v>
+        <v>0.02</v>
       </c>
       <c r="I201" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -8790,29 +8790,29 @@
       </c>
       <c r="C202" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
         </is>
       </c>
       <c r="D202" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду40 Ру25</t>
+          <t>Стакан переборочный Ду10Ру100</t>
         </is>
       </c>
       <c r="E202" s="34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F202" s="35" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G202" s="35" t="n">
         <v>10</v>
       </c>
       <c r="H202" s="36" t="n">
-        <v>0.008</v>
+        <v>0.05</v>
       </c>
       <c r="I202" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -8832,20 +8832,20 @@
       </c>
       <c r="D203" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15</t>
+          <t>Клапан фланцевый угловой Ду40 Ру10</t>
         </is>
       </c>
       <c r="E203" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F203" s="35" t="n">
         <v>10</v>
-      </c>
-      <c r="F203" s="35" t="n">
-        <v>1</v>
       </c>
       <c r="G203" s="35" t="n">
         <v>10</v>
       </c>
       <c r="H203" s="36" t="n">
-        <v>0.015</v>
+        <v>0.008</v>
       </c>
       <c r="I203" s="34" t="inlineStr">
         <is>
@@ -8864,25 +8864,25 @@
       </c>
       <c r="C204" s="34" t="inlineStr">
         <is>
-          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D204" s="33" t="inlineStr">
         <is>
-          <t>Гайка Шторца цапковая Ду50Ру16</t>
+          <t>Клапан фланцевый угловой Ду40 Ру25</t>
         </is>
       </c>
       <c r="E204" s="34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F204" s="35" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G204" s="35" t="n">
         <v>10</v>
       </c>
       <c r="H204" s="36" t="n">
-        <v>0.05</v>
+        <v>0.008</v>
       </c>
       <c r="I204" s="34" t="inlineStr">
         <is>
@@ -8906,24 +8906,24 @@
       </c>
       <c r="D205" s="33" t="inlineStr">
         <is>
-          <t>Судовая запорная арматура</t>
+          <t>Клапан штуцерный угловой Ду15</t>
         </is>
       </c>
       <c r="E205" s="34" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F205" s="35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G205" s="35" t="n">
         <v>10</v>
       </c>
       <c r="H205" s="36" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="I205" s="34" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -8938,29 +8938,29 @@
       </c>
       <c r="C206" s="34" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
         </is>
       </c>
       <c r="D206" s="33" t="inlineStr">
         <is>
-          <t>Скобы разные ( 1 большая+ 2 маленькие )</t>
+          <t>Гайка Шторца цапковая Ду50Ру16</t>
         </is>
       </c>
       <c r="E206" s="34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F206" s="35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G206" s="35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H206" s="36" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="I206" s="34" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -8975,29 +8975,29 @@
       </c>
       <c r="C207" s="34" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D207" s="33" t="inlineStr">
         <is>
-          <t>Регулятор РТНД-150</t>
+          <t>Судовая запорная арматура</t>
         </is>
       </c>
       <c r="E207" s="34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F207" s="35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G207" s="35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H207" s="36" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="I207" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -9012,12 +9012,12 @@
       </c>
       <c r="C208" s="34" t="inlineStr">
         <is>
-          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="D208" s="33" t="inlineStr">
         <is>
-          <t>Компенсатор Ду 150</t>
+          <t>Скобы разные ( 1 большая+ 2 маленькие )</t>
         </is>
       </c>
       <c r="E208" s="34" t="n">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="I208" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="C209" s="34" t="inlineStr">
         <is>
-          <t>Насосы</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="D209" s="33" t="inlineStr">
         <is>
-          <t>РТИ НЦКГ 4/40 ?????для ремонта насоса</t>
+          <t>Регулятор РТНД-150</t>
         </is>
       </c>
       <c r="E209" s="34" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="I209" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -9086,29 +9086,29 @@
       </c>
       <c r="C210" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
         </is>
       </c>
       <c r="D210" s="33" t="inlineStr">
         <is>
-          <t>Пружина плунжера</t>
+          <t>Компенсатор Ду 150</t>
         </is>
       </c>
       <c r="E210" s="34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F210" s="35" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G210" s="35" t="n">
         <v>9</v>
       </c>
       <c r="H210" s="36" t="n">
-        <v>0.003</v>
+        <v>0.03</v>
       </c>
       <c r="I210" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -9123,25 +9123,25 @@
       </c>
       <c r="C211" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Насосы</t>
         </is>
       </c>
       <c r="D211" s="33" t="inlineStr">
         <is>
-          <t>Пружина клапана распределения наружная</t>
+          <t>РТИ НЦКГ 4/40 ?????для ремонта насоса</t>
         </is>
       </c>
       <c r="E211" s="34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F211" s="35" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G211" s="35" t="n">
         <v>9</v>
       </c>
       <c r="H211" s="36" t="n">
-        <v>0.003</v>
+        <v>0.03</v>
       </c>
       <c r="I211" s="34" t="inlineStr">
         <is>
@@ -9165,20 +9165,20 @@
       </c>
       <c r="D212" s="33" t="inlineStr">
         <is>
-          <t>Трубка топливная ВД</t>
+          <t>Пружина плунжера</t>
         </is>
       </c>
       <c r="E212" s="34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F212" s="35" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G212" s="35" t="n">
         <v>9</v>
       </c>
       <c r="H212" s="36" t="n">
-        <v>0.03</v>
+        <v>0.003</v>
       </c>
       <c r="I212" s="34" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D213" s="33" t="inlineStr">
         <is>
-          <t>Шарнир длинный 602-061-222</t>
+          <t>Пружина клапана распределения наружная</t>
         </is>
       </c>
       <c r="E213" s="34" t="n">
@@ -9215,7 +9215,7 @@
         <v>9</v>
       </c>
       <c r="H213" s="36" t="n">
-        <v>0.06</v>
+        <v>0.003</v>
       </c>
       <c r="I213" s="34" t="inlineStr">
         <is>
@@ -9239,20 +9239,20 @@
       </c>
       <c r="D214" s="33" t="inlineStr">
         <is>
-          <t>Шатун VD26/20</t>
+          <t>Трубка топливная ВД</t>
         </is>
       </c>
       <c r="E214" s="34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F214" s="35" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G214" s="35" t="n">
         <v>9</v>
       </c>
       <c r="H214" s="36" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="I214" s="34" t="inlineStr">
         <is>
@@ -9276,20 +9276,20 @@
       </c>
       <c r="D215" s="33" t="inlineStr">
         <is>
-          <t>Кран индикаторный VD26/20</t>
+          <t>Шарнир длинный 602-061-222</t>
         </is>
       </c>
       <c r="E215" s="34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F215" s="35" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G215" s="35" t="n">
         <v>9</v>
       </c>
       <c r="H215" s="36" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="I215" s="34" t="inlineStr">
         <is>
@@ -9313,20 +9313,20 @@
       </c>
       <c r="D216" s="33" t="inlineStr">
         <is>
-          <t>Шестерня импортная S2010-0810-0101</t>
+          <t>Шатун VD26/20</t>
         </is>
       </c>
       <c r="E216" s="34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F216" s="35" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G216" s="35" t="n">
         <v>9</v>
       </c>
       <c r="H216" s="36" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="I216" s="34" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="D217" s="33" t="inlineStr">
         <is>
-          <t>Крышка 6 NVD26 А3</t>
+          <t>Кран индикаторный VD26/20</t>
         </is>
       </c>
       <c r="E217" s="34" t="n">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="I217" s="34" t="inlineStr">
         <is>
-          <t>ЗИП и насосы</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -9382,29 +9382,29 @@
       </c>
       <c r="C218" s="34" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D218" s="33" t="inlineStr">
         <is>
-          <t>Диски тормозные 310мм</t>
+          <t>Шестерня импортная S2010-0810-0101</t>
         </is>
       </c>
       <c r="E218" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F218" s="35" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G218" s="35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H218" s="36" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="I218" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -9419,29 +9419,29 @@
       </c>
       <c r="C219" s="34" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D219" s="33" t="inlineStr">
         <is>
-          <t>Диски тормозные 260мм</t>
+          <t>Крышка 6 NVD26 А3</t>
         </is>
       </c>
       <c r="E219" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F219" s="35" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G219" s="35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H219" s="36" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="I219" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>ЗИП и насосы</t>
         </is>
       </c>
     </row>
@@ -9456,12 +9456,12 @@
       </c>
       <c r="C220" s="34" t="inlineStr">
         <is>
-          <t>Насосы</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="D220" s="33" t="inlineStr">
         <is>
-          <t>Колесо раб.Насос НЦВ 40/80</t>
+          <t>Диски тормозные 310мм</t>
         </is>
       </c>
       <c r="E220" s="34" t="n">
@@ -9493,12 +9493,12 @@
       </c>
       <c r="C221" s="34" t="inlineStr">
         <is>
-          <t>Насосы</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="D221" s="33" t="inlineStr">
         <is>
-          <t>Колесо раб. Насос НЦВ 160/80</t>
+          <t>Диски тормозные 260мм</t>
         </is>
       </c>
       <c r="E221" s="34" t="n">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="D222" s="33" t="inlineStr">
         <is>
-          <t>Колесо рабочее для Насос НЦВ 40/20</t>
+          <t>Колесо раб.Насос НЦВ 40/80</t>
         </is>
       </c>
       <c r="E222" s="34" t="n">
@@ -9567,29 +9567,29 @@
       </c>
       <c r="C223" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Насосы</t>
         </is>
       </c>
       <c r="D223" s="33" t="inlineStr">
         <is>
-          <t>Кольцо уплотнительное 20,22х3,53</t>
+          <t>Колесо раб. Насос НЦВ 160/80</t>
         </is>
       </c>
       <c r="E223" s="34" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="F223" s="35" t="n">
-        <v>0.1</v>
+        <v>8</v>
       </c>
       <c r="G223" s="35" t="n">
         <v>8</v>
       </c>
       <c r="H223" s="36" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="I223" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -9604,19 +9604,19 @@
       </c>
       <c r="C224" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Насосы</t>
         </is>
       </c>
       <c r="D224" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду20 Ру100</t>
+          <t>Колесо рабочее для Насос НЦВ 40/20</t>
         </is>
       </c>
       <c r="E224" s="34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F224" s="35" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="G224" s="35" t="n">
         <v>8</v>
@@ -9626,7 +9626,7 @@
       </c>
       <c r="I224" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -9641,29 +9641,29 @@
       </c>
       <c r="C225" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D225" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру10</t>
+          <t>Кольцо уплотнительное 20,22х3,53</t>
         </is>
       </c>
       <c r="E225" s="34" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="F225" s="35" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="G225" s="35" t="n">
         <v>8</v>
       </c>
       <c r="H225" s="36" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="I225" s="34" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -9683,24 +9683,24 @@
       </c>
       <c r="D226" s="33" t="inlineStr">
         <is>
-          <t>Клапан предохранит. фланцевый угловой Ду32Ру4 (524-03.090)</t>
+          <t>Клапан штуцерный угловой Ду20 Ру100</t>
         </is>
       </c>
       <c r="E226" s="34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F226" s="35" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="G226" s="35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H226" s="36" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="I226" s="34" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -9720,24 +9720,24 @@
       </c>
       <c r="D227" s="33" t="inlineStr">
         <is>
-          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50 Ру6</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру10</t>
         </is>
       </c>
       <c r="E227" s="34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F227" s="35" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="G227" s="35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H227" s="36" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="I227" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="D228" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру10</t>
+          <t>Клапан предохранит. фланцевый угловой Ду32Ру4 (524-03.090)</t>
         </is>
       </c>
       <c r="E228" s="34" t="n">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="I228" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -9794,20 +9794,20 @@
       </c>
       <c r="D229" s="33" t="inlineStr">
         <is>
-          <t>Кран трехходовой штуцерный Ду32 Ру10</t>
+          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50 Ру6</t>
         </is>
       </c>
       <c r="E229" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F229" s="35" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="G229" s="35" t="n">
         <v>7</v>
       </c>
       <c r="H229" s="36" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="I229" s="34" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="D230" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной ДУ32 Ру25 (сталь)</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру10</t>
         </is>
       </c>
       <c r="E230" s="34" t="n">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="I230" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -9868,24 +9868,24 @@
       </c>
       <c r="D231" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15Ру100</t>
+          <t>Кран трехходовой штуцерный Ду32 Ру10</t>
         </is>
       </c>
       <c r="E231" s="34" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F231" s="35" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="G231" s="35" t="n">
         <v>7</v>
       </c>
       <c r="H231" s="36" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="I231" s="34" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -9905,24 +9905,24 @@
       </c>
       <c r="D232" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32 Ру100</t>
+          <t>Клапан фланцевый проходной ДУ32 Ру25 (сталь)</t>
         </is>
       </c>
       <c r="E232" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F232" s="35" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="G232" s="35" t="n">
         <v>7</v>
       </c>
       <c r="H232" s="36" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="I232" s="34" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -9942,20 +9942,20 @@
       </c>
       <c r="D233" s="33" t="inlineStr">
         <is>
-          <t>Клапан Пожарный фланцевый угловой Ду32</t>
+          <t>Клапан штуцерный угловой Ду15Ру100</t>
         </is>
       </c>
       <c r="E233" s="34" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F233" s="35" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G233" s="35" t="n">
         <v>7</v>
       </c>
       <c r="H233" s="36" t="n">
-        <v>0.005</v>
+        <v>0.011</v>
       </c>
       <c r="I233" s="34" t="inlineStr">
         <is>
@@ -9974,29 +9974,29 @@
       </c>
       <c r="C234" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D234" s="33" t="inlineStr">
         <is>
-          <t>Кольцо уплотнительное 26,0х7,0</t>
+          <t>Клапан штуцерный угловой Ду32 Ру100</t>
         </is>
       </c>
       <c r="E234" s="34" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="F234" s="35" t="n">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
       <c r="G234" s="35" t="n">
         <v>7</v>
       </c>
       <c r="H234" s="36" t="n">
-        <v>0.035</v>
+        <v>0.01</v>
       </c>
       <c r="I234" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -10011,29 +10011,29 @@
       </c>
       <c r="C235" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D235" s="33" t="inlineStr">
         <is>
-          <t>Кольцо уплотнительное 40,65х5,33</t>
+          <t>Клапан Пожарный фланцевый угловой Ду32</t>
         </is>
       </c>
       <c r="E235" s="34" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="F235" s="35" t="n">
-        <v>0.1</v>
+        <v>7</v>
       </c>
       <c r="G235" s="35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H235" s="36" t="n">
-        <v>0.03</v>
+        <v>0.005</v>
       </c>
       <c r="I235" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -10048,29 +10048,29 @@
       </c>
       <c r="C236" s="34" t="inlineStr">
         <is>
-          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D236" s="33" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду20Ру100</t>
+          <t>Кольцо уплотнительное 26,0х7,0</t>
         </is>
       </c>
       <c r="E236" s="34" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="F236" s="35" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="G236" s="35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H236" s="36" t="n">
-        <v>0.03</v>
+        <v>0.035</v>
       </c>
       <c r="I236" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -10085,29 +10085,29 @@
       </c>
       <c r="C237" s="34" t="inlineStr">
         <is>
-          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D237" s="33" t="inlineStr">
         <is>
-          <t>Компенсатор Ду 200 Ру2,5</t>
+          <t>Кольцо уплотнительное 40,65х5,33</t>
         </is>
       </c>
       <c r="E237" s="34" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F237" s="35" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="G237" s="35" t="n">
         <v>6</v>
       </c>
       <c r="H237" s="36" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="I237" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -10122,29 +10122,29 @@
       </c>
       <c r="C238" s="34" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
         </is>
       </c>
       <c r="D238" s="33" t="inlineStr">
         <is>
-          <t>Вентилятор РСС-10/10</t>
+          <t>Стакан переборочный Ду20Ру100</t>
         </is>
       </c>
       <c r="E238" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F238" s="35" t="n">
         <v>2</v>
-      </c>
-      <c r="F238" s="35" t="n">
-        <v>3</v>
       </c>
       <c r="G238" s="35" t="n">
         <v>6</v>
       </c>
       <c r="H238" s="36" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="I238" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -10159,12 +10159,12 @@
       </c>
       <c r="C239" s="34" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
         </is>
       </c>
       <c r="D239" s="33" t="inlineStr">
         <is>
-          <t>Вентилятор ЦСУ-14</t>
+          <t>Компенсатор Ду 200 Ру2,5</t>
         </is>
       </c>
       <c r="E239" s="34" t="n">
@@ -10196,25 +10196,25 @@
       </c>
       <c r="C240" s="34" t="inlineStr">
         <is>
-          <t>Насосы</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="D240" s="33" t="inlineStr">
         <is>
-          <t>Втулка насоса НЦВ 100/30</t>
+          <t>Вентилятор РСС-10/10</t>
         </is>
       </c>
       <c r="E240" s="34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F240" s="35" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G240" s="35" t="n">
         <v>6</v>
       </c>
       <c r="H240" s="36" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="I240" s="34" t="inlineStr">
         <is>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="C241" s="34" t="inlineStr">
         <is>
-          <t>Насосы</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="D241" s="33" t="inlineStr">
         <is>
-          <t>Сальниковая обойма нижняя часть НЦВС 63/20</t>
+          <t>Вентилятор ЦСУ-14</t>
         </is>
       </c>
       <c r="E241" s="34" t="n">
@@ -10270,25 +10270,25 @@
       </c>
       <c r="C242" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Насосы</t>
         </is>
       </c>
       <c r="D242" s="33" t="inlineStr">
         <is>
-          <t>Клапан всасывающий</t>
+          <t>Втулка насоса НЦВ 100/30</t>
         </is>
       </c>
       <c r="E242" s="34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F242" s="35" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G242" s="35" t="n">
         <v>6</v>
       </c>
       <c r="H242" s="36" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="I242" s="34" t="inlineStr">
         <is>
@@ -10307,29 +10307,29 @@
       </c>
       <c r="C243" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Насосы</t>
         </is>
       </c>
       <c r="D243" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20</t>
+          <t>Сальниковая обойма нижняя часть НЦВС 63/20</t>
         </is>
       </c>
       <c r="E243" s="34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F243" s="35" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G243" s="35" t="n">
         <v>6</v>
       </c>
       <c r="H243" s="36" t="n">
-        <v>0.008</v>
+        <v>0.02</v>
       </c>
       <c r="I243" s="34" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -10344,29 +10344,29 @@
       </c>
       <c r="C244" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D244" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+          <t>Клапан всасывающий</t>
         </is>
       </c>
       <c r="E244" s="34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F244" s="35" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G244" s="35" t="n">
         <v>6</v>
       </c>
       <c r="H244" s="36" t="n">
-        <v>0.008</v>
+        <v>0.02</v>
       </c>
       <c r="I244" s="34" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -10386,20 +10386,20 @@
       </c>
       <c r="D245" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15Ру100</t>
+          <t>Клапан штуцерный проходной Ду 20</t>
         </is>
       </c>
       <c r="E245" s="34" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F245" s="35" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G245" s="35" t="n">
         <v>6</v>
       </c>
       <c r="H245" s="36" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="I245" s="34" t="inlineStr">
         <is>
@@ -10418,29 +10418,29 @@
       </c>
       <c r="C246" s="34" t="inlineStr">
         <is>
-          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D246" s="33" t="inlineStr">
         <is>
-          <t>Ствол пожарный Ду65 Ру10 черт.812-03.011-02</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
       <c r="E246" s="34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F246" s="35" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G246" s="35" t="n">
         <v>6</v>
       </c>
       <c r="H246" s="36" t="n">
-        <v>0.02</v>
+        <v>0.008</v>
       </c>
       <c r="I246" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -10455,29 +10455,29 @@
       </c>
       <c r="C247" s="34" t="inlineStr">
         <is>
-          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D247" s="33" t="inlineStr">
         <is>
-          <t>Ствол пожарный Ду50 Ру10 черт.812-03.011-01</t>
+          <t>Клапан штуцерный угловой Ду15Ру100</t>
         </is>
       </c>
       <c r="E247" s="34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F247" s="35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G247" s="35" t="n">
         <v>6</v>
       </c>
       <c r="H247" s="36" t="n">
-        <v>0.02</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I247" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -10492,12 +10492,12 @@
       </c>
       <c r="C248" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
         </is>
       </c>
       <c r="D248" s="33" t="inlineStr">
         <is>
-          <t>Коллектор (паук) 602-205-014</t>
+          <t>Ствол пожарный Ду65 Ру10 черт.812-03.011-02</t>
         </is>
       </c>
       <c r="E248" s="34" t="n">
@@ -10529,25 +10529,25 @@
       </c>
       <c r="C249" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
         </is>
       </c>
       <c r="D249" s="33" t="inlineStr">
         <is>
-          <t>Ось коромысла 602-061-221</t>
+          <t>Ствол пожарный Ду50 Ру10 черт.812-03.011-01</t>
         </is>
       </c>
       <c r="E249" s="34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F249" s="35" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G249" s="35" t="n">
         <v>6</v>
       </c>
       <c r="H249" s="36" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="I249" s="34" t="inlineStr">
         <is>
@@ -10571,20 +10571,20 @@
       </c>
       <c r="D250" s="33" t="inlineStr">
         <is>
-          <t>Плунжерная пара</t>
+          <t>Коллектор (паук) 602-205-014</t>
         </is>
       </c>
       <c r="E250" s="34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F250" s="35" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G250" s="35" t="n">
         <v>6</v>
       </c>
       <c r="H250" s="36" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="I250" s="34" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
       </c>
       <c r="D251" s="33" t="inlineStr">
         <is>
-          <t>Ролик толкателя</t>
+          <t>Ось коромысла 602-061-221</t>
         </is>
       </c>
       <c r="E251" s="34" t="n">
@@ -10645,20 +10645,20 @@
       </c>
       <c r="D252" s="33" t="inlineStr">
         <is>
-          <t>Крышки цилиндра VD26/20 (в сборе)</t>
+          <t>Плунжерная пара</t>
         </is>
       </c>
       <c r="E252" s="34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F252" s="35" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G252" s="35" t="n">
         <v>6</v>
       </c>
       <c r="H252" s="36" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="I252" s="34" t="inlineStr">
         <is>
@@ -10682,20 +10682,20 @@
       </c>
       <c r="D253" s="33" t="inlineStr">
         <is>
-          <t>Крышки цилиндра VD26/20 (голые)</t>
+          <t>Ролик толкателя</t>
         </is>
       </c>
       <c r="E253" s="34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F253" s="35" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G253" s="35" t="n">
         <v>6</v>
       </c>
       <c r="H253" s="36" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="I253" s="34" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="D254" s="33" t="inlineStr">
         <is>
-          <t>Шестерня демпферная</t>
+          <t>Крышки цилиндра VD26/20 (в сборе)</t>
         </is>
       </c>
       <c r="E254" s="34" t="n">
@@ -10756,20 +10756,20 @@
       </c>
       <c r="D255" s="33" t="inlineStr">
         <is>
-          <t>Кольцо уплотнительное 66,52х5,33</t>
+          <t>Крышки цилиндра VD26/20 (голые)</t>
         </is>
       </c>
       <c r="E255" s="34" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="F255" s="35" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="G255" s="35" t="n">
         <v>6</v>
       </c>
       <c r="H255" s="36" t="n">
-        <v>0.029</v>
+        <v>0.02</v>
       </c>
       <c r="I255" s="34" t="inlineStr">
         <is>
@@ -10793,24 +10793,24 @@
       </c>
       <c r="D256" s="33" t="inlineStr">
         <is>
-          <t>Кольцо к/с ,**511-26702</t>
+          <t>Шестерня демпферная</t>
         </is>
       </c>
       <c r="E256" s="34" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="F256" s="35" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="G256" s="35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H256" s="36" t="n">
-        <v>0.027</v>
+        <v>0.02</v>
       </c>
       <c r="I256" s="34" t="inlineStr">
         <is>
-          <t>ЗИП и насосы</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -10830,20 +10830,20 @@
       </c>
       <c r="D257" s="33" t="inlineStr">
         <is>
-          <t>Кольцо уплотнительное 26,2х3,63</t>
+          <t>Кольцо уплотнительное 66,52х5,33</t>
         </is>
       </c>
       <c r="E257" s="34" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F257" s="35" t="n">
         <v>0.1</v>
       </c>
       <c r="G257" s="35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H257" s="36" t="n">
-        <v>0.026</v>
+        <v>0.029</v>
       </c>
       <c r="I257" s="34" t="inlineStr">
         <is>
@@ -10862,29 +10862,29 @@
       </c>
       <c r="C258" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D258" s="33" t="inlineStr">
         <is>
-          <t>Клапан с электромагнитным ручным управлением Ду20/10 перем. 220В</t>
+          <t>Кольцо к/с ,**511-26702</t>
         </is>
       </c>
       <c r="E258" s="34" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="F258" s="35" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="G258" s="35" t="n">
         <v>5</v>
       </c>
       <c r="H258" s="36" t="n">
-        <v>0.002</v>
+        <v>0.027</v>
       </c>
       <c r="I258" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>ЗИП и насосы</t>
         </is>
       </c>
     </row>
@@ -10899,29 +10899,29 @@
       </c>
       <c r="C259" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D259" s="33" t="inlineStr">
         <is>
-          <t>Клапан</t>
+          <t>Кольцо уплотнительное 26,2х3,63</t>
         </is>
       </c>
       <c r="E259" s="34" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="F259" s="35" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="G259" s="35" t="n">
         <v>5</v>
       </c>
       <c r="H259" s="36" t="n">
-        <v>0.01</v>
+        <v>0.026</v>
       </c>
       <c r="I259" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -10941,20 +10941,20 @@
       </c>
       <c r="D260" s="33" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду25Ру16</t>
+          <t>Клапан с электромагнитным ручным управлением Ду20/10 перем. 220В</t>
         </is>
       </c>
       <c r="E260" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F260" s="35" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G260" s="35" t="n">
         <v>5</v>
       </c>
       <c r="H260" s="36" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="I260" s="34" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
       </c>
       <c r="D261" s="33" t="inlineStr">
         <is>
-          <t>Клапан паровой Ду65Ру10</t>
+          <t>Клапан</t>
         </is>
       </c>
       <c r="E261" s="34" t="n">
@@ -10991,7 +10991,7 @@
         <v>5</v>
       </c>
       <c r="H261" s="36" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I261" s="34" t="inlineStr">
         <is>
@@ -11015,20 +11015,20 @@
       </c>
       <c r="D262" s="33" t="inlineStr">
         <is>
-          <t>Сетка на фильтр Ду20 маленькая</t>
+          <t>Клапан муфтовый проходной запорный Ду25Ру16</t>
         </is>
       </c>
       <c r="E262" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F262" s="35" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G262" s="35" t="n">
         <v>5</v>
       </c>
       <c r="H262" s="36" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="I262" s="34" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
       </c>
       <c r="D263" s="33" t="inlineStr">
         <is>
-          <t>Кланан Рр18-2 45/25</t>
+          <t>Клапан паровой Ду65Ру10</t>
         </is>
       </c>
       <c r="E263" s="34" t="n">
@@ -11065,7 +11065,7 @@
         <v>5</v>
       </c>
       <c r="H263" s="36" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I263" s="34" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
       </c>
       <c r="D264" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной ДУ25 ???</t>
+          <t>Кланан Рр18-2 45/25</t>
         </is>
       </c>
       <c r="E264" s="34" t="n">
@@ -11102,11 +11102,11 @@
         <v>5</v>
       </c>
       <c r="H264" s="36" t="n">
-        <v>0.003</v>
+        <v>0.01</v>
       </c>
       <c r="I264" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -11126,24 +11126,24 @@
       </c>
       <c r="D265" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду25 Ру100</t>
+          <t>Клапан фланцевый проходной ДУ25 ???</t>
         </is>
       </c>
       <c r="E265" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F265" s="35" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G265" s="35" t="n">
         <v>5</v>
       </c>
       <c r="H265" s="36" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="I265" s="34" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -11163,24 +11163,24 @@
       </c>
       <c r="D266" s="33" t="inlineStr">
         <is>
-          <t>Фильтр забортной воды Ду 50</t>
+          <t>Клапан штуцерный угловой Ду25 Ру100</t>
         </is>
       </c>
       <c r="E266" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F266" s="35" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G266" s="35" t="n">
         <v>5</v>
       </c>
       <c r="H266" s="36" t="n">
-        <v>0.012</v>
+        <v>0.006</v>
       </c>
       <c r="I266" s="34" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -11195,29 +11195,29 @@
       </c>
       <c r="C267" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D267" s="33" t="inlineStr">
         <is>
-          <t>Фильтр забортной воды Ду 100</t>
+          <t>Кольцо уплотнительное 34,5х3,53</t>
         </is>
       </c>
       <c r="E267" s="34" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F267" s="35" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="G267" s="35" t="n">
         <v>5</v>
       </c>
       <c r="H267" s="36" t="n">
-        <v>0.045</v>
+        <v>0.025</v>
       </c>
       <c r="I267" s="34" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -11232,29 +11232,29 @@
       </c>
       <c r="C268" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D268" s="33" t="inlineStr">
         <is>
-          <t>Кольцо уплотнительное 34,5х3,53</t>
+          <t>Кран двухходовой штуцерный Ду20 Ру16</t>
         </is>
       </c>
       <c r="E268" s="34" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="F268" s="35" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="G268" s="35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H268" s="36" t="n">
-        <v>0.025</v>
+        <v>0.006</v>
       </c>
       <c r="I268" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11274,7 @@
       </c>
       <c r="D269" s="33" t="inlineStr">
         <is>
-          <t>Кран двухходовой штуцерный Ду20 Ру16</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
       <c r="E269" s="34" t="n">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="I269" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -11311,7 +11311,7 @@
       </c>
       <c r="D270" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
       <c r="E270" s="34" t="n">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="D271" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Клапан штуцерный угловой Ду20 Ру160</t>
         </is>
       </c>
       <c r="E271" s="34" t="n">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="C272" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D272" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду20 Ру160</t>
+          <t>Вкладыш мотылевый 3РР</t>
         </is>
       </c>
       <c r="E272" s="34" t="n">
@@ -11398,11 +11398,11 @@
         <v>4</v>
       </c>
       <c r="H272" s="36" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="I272" s="34" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -11422,7 +11422,7 @@
       </c>
       <c r="D273" s="33" t="inlineStr">
         <is>
-          <t>Вкладыш мотылевый 3РР</t>
+          <t>Вкладыш рамовый номинал</t>
         </is>
       </c>
       <c r="E273" s="34" t="n">
@@ -11459,7 +11459,7 @@
       </c>
       <c r="D274" s="33" t="inlineStr">
         <is>
-          <t>Вкладыш рамовый номинал</t>
+          <t>Ударник короткий</t>
         </is>
       </c>
       <c r="E274" s="34" t="n">
@@ -11472,7 +11472,7 @@
         <v>4</v>
       </c>
       <c r="H274" s="36" t="n">
-        <v>0.002</v>
+        <v>0.03</v>
       </c>
       <c r="I274" s="34" t="inlineStr">
         <is>
@@ -11496,20 +11496,20 @@
       </c>
       <c r="D275" s="33" t="inlineStr">
         <is>
-          <t>Ударник короткий</t>
+          <t>Кольцо уплотнительное 46,99х5,33</t>
         </is>
       </c>
       <c r="E275" s="34" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="F275" s="35" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="G275" s="35" t="n">
         <v>4</v>
       </c>
       <c r="H275" s="36" t="n">
-        <v>0.03</v>
+        <v>0.022</v>
       </c>
       <c r="I275" s="34" t="inlineStr">
         <is>
@@ -11533,20 +11533,20 @@
       </c>
       <c r="D276" s="33" t="inlineStr">
         <is>
-          <t>Кольцо уплотнительное 46,99х5,33</t>
+          <t>Штанга VD26/20</t>
         </is>
       </c>
       <c r="E276" s="34" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="F276" s="35" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="G276" s="35" t="n">
         <v>4</v>
       </c>
       <c r="H276" s="36" t="n">
-        <v>0.022</v>
+        <v>0.03</v>
       </c>
       <c r="I276" s="34" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="D277" s="33" t="inlineStr">
         <is>
-          <t>Штанга VD26/20</t>
+          <t>Пружина клапана VD26/20</t>
         </is>
       </c>
       <c r="E277" s="34" t="n">
@@ -11583,7 +11583,7 @@
         <v>4</v>
       </c>
       <c r="H277" s="36" t="n">
-        <v>0.03</v>
+        <v>0.002</v>
       </c>
       <c r="I277" s="34" t="inlineStr">
         <is>
@@ -11602,29 +11602,29 @@
       </c>
       <c r="C278" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D278" s="33" t="inlineStr">
         <is>
-          <t>Пружина клапана VD26/20</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
         </is>
       </c>
       <c r="E278" s="34" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F278" s="35" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="G278" s="35" t="n">
         <v>4</v>
       </c>
       <c r="H278" s="36" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="I278" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -11644,20 +11644,20 @@
       </c>
       <c r="D279" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
+          <t>Клапан штуцерный угловой Ду15 Ру160</t>
         </is>
       </c>
       <c r="E279" s="34" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F279" s="35" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="G279" s="35" t="n">
         <v>4</v>
       </c>
       <c r="H279" s="36" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="I279" s="34" t="inlineStr">
         <is>
@@ -11676,25 +11676,25 @@
       </c>
       <c r="C280" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
         </is>
       </c>
       <c r="D280" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15 Ру160</t>
+          <t>Стакан переборочный Ду25Ру100</t>
         </is>
       </c>
       <c r="E280" s="34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F280" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G280" s="35" t="n">
         <v>4</v>
       </c>
       <c r="H280" s="36" t="n">
-        <v>0.006</v>
+        <v>0.02</v>
       </c>
       <c r="I280" s="34" t="inlineStr">
         <is>
@@ -11713,25 +11713,25 @@
       </c>
       <c r="C281" s="34" t="inlineStr">
         <is>
-          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D281" s="33" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду25Ру100</t>
+          <t>Кран штуцерный спусковой самозапорный проходной Ду15 Ру25</t>
         </is>
       </c>
       <c r="E281" s="34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F281" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G281" s="35" t="n">
         <v>4</v>
       </c>
       <c r="H281" s="36" t="n">
-        <v>0.02</v>
+        <v>0.006</v>
       </c>
       <c r="I281" s="34" t="inlineStr">
         <is>
@@ -11755,20 +11755,20 @@
       </c>
       <c r="D282" s="33" t="inlineStr">
         <is>
-          <t>Кран штуцерный спусковой самозапорный проходной Ду15 Ру25</t>
+          <t>Кран двухходовой фланцевый Ду32 Ру6</t>
         </is>
       </c>
       <c r="E282" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F282" s="35" t="n">
         <v>4</v>
-      </c>
-      <c r="F282" s="35" t="n">
-        <v>1</v>
       </c>
       <c r="G282" s="35" t="n">
         <v>4</v>
       </c>
       <c r="H282" s="36" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="I282" s="34" t="inlineStr">
         <is>
@@ -11787,29 +11787,29 @@
       </c>
       <c r="C283" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
         </is>
       </c>
       <c r="D283" s="33" t="inlineStr">
         <is>
-          <t>Кран двухходовой фланцевый Ду32 Ру6</t>
+          <t>Гайка Ротта цапковая Ду65Ру10</t>
         </is>
       </c>
       <c r="E283" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F283" s="35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G283" s="35" t="n">
         <v>4</v>
       </c>
       <c r="H283" s="36" t="n">
-        <v>0.005</v>
+        <v>0.02</v>
       </c>
       <c r="I283" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -11824,29 +11824,29 @@
       </c>
       <c r="C284" s="34" t="inlineStr">
         <is>
-          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D284" s="33" t="inlineStr">
         <is>
-          <t>Гайка Ротта цапковая Ду65Ру10</t>
+          <t>Клапан штуцерный угловой Ду15 Ру160</t>
         </is>
       </c>
       <c r="E284" s="34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F284" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G284" s="35" t="n">
         <v>4</v>
       </c>
       <c r="H284" s="36" t="n">
-        <v>0.02</v>
+        <v>0.006</v>
       </c>
       <c r="I284" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -11861,29 +11861,29 @@
       </c>
       <c r="C285" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D285" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15 Ру160</t>
+          <t>Кольцо уплотнительное 44,2х3,0</t>
         </is>
       </c>
       <c r="E285" s="34" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F285" s="35" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G285" s="35" t="n">
         <v>4</v>
       </c>
       <c r="H285" s="36" t="n">
-        <v>0.006</v>
+        <v>0.018</v>
       </c>
       <c r="I285" s="34" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -11898,29 +11898,29 @@
       </c>
       <c r="C286" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D286" s="33" t="inlineStr">
         <is>
-          <t>Кольцо уплотнительное 44,2х3,0</t>
+          <t>Клапан запорный штуцерный проходной Ду10 Ру16</t>
         </is>
       </c>
       <c r="E286" s="34" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="F286" s="35" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="G286" s="35" t="n">
         <v>4</v>
       </c>
       <c r="H286" s="36" t="n">
-        <v>0.018</v>
+        <v>0.006</v>
       </c>
       <c r="I286" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="D287" s="33" t="inlineStr">
         <is>
-          <t>Клапан запорный штуцерный проходной Ду10 Ру16</t>
+          <t>Клапан штуцерный угловой Ду10 Р160</t>
         </is>
       </c>
       <c r="E287" s="34" t="n">
@@ -11977,20 +11977,20 @@
       </c>
       <c r="D288" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду10 Р160</t>
+          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
         </is>
       </c>
       <c r="E288" s="34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F288" s="35" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="G288" s="35" t="n">
         <v>4</v>
       </c>
       <c r="H288" s="36" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="I288" s="34" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
       </c>
       <c r="D290" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
+          <t>Клапан муфтовый проходной запорный Ду32Ру10</t>
         </is>
       </c>
       <c r="E290" s="34" t="n">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="D291" s="33" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду32Ру10</t>
+          <t>Клапан штуцерный угловой Ду32 Ру100</t>
         </is>
       </c>
       <c r="E291" s="34" t="n">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="I291" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -12120,29 +12120,29 @@
       </c>
       <c r="C292" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="D292" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32 Ру100</t>
+          <t>Противовес 3,2т (Россия)</t>
         </is>
       </c>
       <c r="E292" s="34" t="n">
         <v>1</v>
       </c>
       <c r="F292" s="35" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G292" s="35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H292" s="36" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="I292" s="34" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -12162,7 +12162,7 @@
       </c>
       <c r="D293" s="33" t="inlineStr">
         <is>
-          <t>Противовес 3,2т (Россия)</t>
+          <t>Гак</t>
         </is>
       </c>
       <c r="E293" s="34" t="n">
@@ -12194,12 +12194,12 @@
       </c>
       <c r="C294" s="34" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D294" s="33" t="inlineStr">
         <is>
-          <t>Гак</t>
+          <t>Двигатель б/у на лапах</t>
         </is>
       </c>
       <c r="E294" s="34" t="n">
@@ -12231,12 +12231,12 @@
       </c>
       <c r="C295" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="D295" s="33" t="inlineStr">
         <is>
-          <t>Двигатель б/у на лапах</t>
+          <t>Противовес 3,2т (Корея)</t>
         </is>
       </c>
       <c r="E295" s="34" t="n">
@@ -12268,29 +12268,29 @@
       </c>
       <c r="C296" s="34" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D296" s="33" t="inlineStr">
         <is>
-          <t>Противовес 3,2т (Корея)</t>
+          <t>Клапан штуцерный проходной невозвратный Ду10Ру100</t>
         </is>
       </c>
       <c r="E296" s="34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F296" s="35" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="G296" s="35" t="n">
         <v>3</v>
       </c>
       <c r="H296" s="36" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="I296" s="34" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -12310,14 +12310,14 @@
       </c>
       <c r="D297" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной невозвратный Ду10Ру100</t>
+          <t>Клапан штуцерный проходной бессальниковый Ду15/1</t>
         </is>
       </c>
       <c r="E297" s="34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F297" s="35" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="G297" s="35" t="n">
         <v>3</v>
@@ -12347,20 +12347,20 @@
       </c>
       <c r="D298" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной бессальниковый Ду15/1</t>
+          <t>Клапан невозв-запор.цапковый угловой под дюрит Ду20Ру6</t>
         </is>
       </c>
       <c r="E298" s="34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F298" s="35" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G298" s="35" t="n">
         <v>3</v>
       </c>
       <c r="H298" s="36" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="I298" s="34" t="inlineStr">
         <is>
@@ -12379,25 +12379,25 @@
       </c>
       <c r="C299" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="D299" s="33" t="inlineStr">
         <is>
-          <t>Клапан невозв-запор.цапковый угловой под дюрит Ду20Ру6</t>
+          <t>Эжектор ВЭЖ 6,3</t>
         </is>
       </c>
       <c r="E299" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F299" s="35" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G299" s="35" t="n">
         <v>3</v>
       </c>
       <c r="H299" s="36" t="n">
-        <v>0.004</v>
+        <v>0.01</v>
       </c>
       <c r="I299" s="34" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
       </c>
       <c r="D300" s="33" t="inlineStr">
         <is>
-          <t>Эжектор ВЭЖ 6,3</t>
+          <t>Вентилятор РСС 2/4</t>
         </is>
       </c>
       <c r="E300" s="34" t="n">
@@ -12438,7 +12438,7 @@
       </c>
       <c r="I300" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -12453,12 +12453,12 @@
       </c>
       <c r="C301" s="34" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D301" s="33" t="inlineStr">
         <is>
-          <t>Вентилятор РСС 2/4</t>
+          <t>Данфас TF-2 -40/+10С R12</t>
         </is>
       </c>
       <c r="E301" s="34" t="n">
@@ -12490,25 +12490,25 @@
       </c>
       <c r="C302" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Насосы</t>
         </is>
       </c>
       <c r="D302" s="33" t="inlineStr">
         <is>
-          <t>Данфас TF-2 -40/+10С R12</t>
+          <t>Шайба стопорная для Насос НЦВ 40/20</t>
         </is>
       </c>
       <c r="E302" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F302" s="35" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G302" s="35" t="n">
         <v>3</v>
       </c>
       <c r="H302" s="36" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="I302" s="34" t="inlineStr">
         <is>
@@ -12527,25 +12527,25 @@
       </c>
       <c r="C303" s="34" t="inlineStr">
         <is>
-          <t>Насосы</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D303" s="33" t="inlineStr">
         <is>
-          <t>Шайба стопорная для Насос НЦВ 40/20</t>
+          <t>Фонарь выхлопной 8NVD48A2U</t>
         </is>
       </c>
       <c r="E303" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F303" s="35" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G303" s="35" t="n">
         <v>3</v>
       </c>
       <c r="H303" s="36" t="n">
-        <v>0.001</v>
+        <v>0.01</v>
       </c>
       <c r="I303" s="34" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="D304" s="33" t="inlineStr">
         <is>
-          <t>Фонарь выхлопной 8NVD48A2U</t>
+          <t>Корпус выхлопного клапана</t>
         </is>
       </c>
       <c r="E304" s="34" t="n">
@@ -12606,20 +12606,20 @@
       </c>
       <c r="D305" s="33" t="inlineStr">
         <is>
-          <t>Корпус выхлопного клапана</t>
+          <t>Плунжерная пара 1ая/2ая модель</t>
         </is>
       </c>
       <c r="E305" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F305" s="35" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G305" s="35" t="n">
         <v>3</v>
       </c>
       <c r="H305" s="36" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I305" s="34" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
       </c>
       <c r="D306" s="33" t="inlineStr">
         <is>
-          <t>Плунжерная пара 1ая/2ая модель</t>
+          <t>Направляющая клапана</t>
         </is>
       </c>
       <c r="E306" s="34" t="n">
@@ -12680,20 +12680,20 @@
       </c>
       <c r="D307" s="33" t="inlineStr">
         <is>
-          <t>Направляющая клапана</t>
+          <t>Клапан пусковой</t>
         </is>
       </c>
       <c r="E307" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F307" s="35" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G307" s="35" t="n">
         <v>3</v>
       </c>
       <c r="H307" s="36" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I307" s="34" t="inlineStr">
         <is>
@@ -12717,20 +12717,20 @@
       </c>
       <c r="D308" s="33" t="inlineStr">
         <is>
-          <t>Клапан пусковой</t>
+          <t>Кулачковая шайба топливная</t>
         </is>
       </c>
       <c r="E308" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F308" s="35" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G308" s="35" t="n">
         <v>3</v>
       </c>
       <c r="H308" s="36" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="I308" s="34" t="inlineStr">
         <is>
@@ -12749,29 +12749,29 @@
       </c>
       <c r="C309" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D309" s="33" t="inlineStr">
         <is>
-          <t>Кулачковая шайба топливная</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
         </is>
       </c>
       <c r="E309" s="34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F309" s="35" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="G309" s="35" t="n">
         <v>3</v>
       </c>
       <c r="H309" s="36" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="I309" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -12791,20 +12791,20 @@
       </c>
       <c r="D310" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
       <c r="E310" s="34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F310" s="35" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="G310" s="35" t="n">
         <v>3</v>
       </c>
       <c r="H310" s="36" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="I310" s="34" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
       </c>
       <c r="D311" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
       <c r="E311" s="34" t="n">
@@ -12939,20 +12939,20 @@
       </c>
       <c r="D314" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Клапан штуцерный угловой Ду15Ру100</t>
         </is>
       </c>
       <c r="E314" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F314" s="35" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G314" s="35" t="n">
         <v>3</v>
       </c>
       <c r="H314" s="36" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="I314" s="34" t="inlineStr">
         <is>
@@ -12976,20 +12976,20 @@
       </c>
       <c r="D315" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15Ру100</t>
+          <t>Клапан штуцерный угловой Ду20 ру 40</t>
         </is>
       </c>
       <c r="E315" s="34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F315" s="35" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G315" s="35" t="n">
         <v>3</v>
       </c>
       <c r="H315" s="36" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="I315" s="34" t="inlineStr">
         <is>
@@ -13013,20 +13013,20 @@
       </c>
       <c r="D316" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду20 ру 40</t>
+          <t>Клапан штуцерный угловой Ду15 Ру100</t>
         </is>
       </c>
       <c r="E316" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F316" s="35" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G316" s="35" t="n">
         <v>3</v>
       </c>
       <c r="H316" s="36" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="I316" s="34" t="inlineStr">
         <is>
@@ -13082,29 +13082,29 @@
       </c>
       <c r="C318" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D318" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15 Ру100</t>
+          <t>Вкладыш мотылевый номинал</t>
         </is>
       </c>
       <c r="E318" s="34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F318" s="35" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G318" s="35" t="n">
         <v>3</v>
       </c>
       <c r="H318" s="36" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="I318" s="34" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -13124,20 +13124,20 @@
       </c>
       <c r="D319" s="33" t="inlineStr">
         <is>
-          <t>Вкладыш мотылевый номинал</t>
+          <t>Клапан выпускной 602-062-001</t>
         </is>
       </c>
       <c r="E319" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F319" s="35" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G319" s="35" t="n">
         <v>3</v>
       </c>
       <c r="H319" s="36" t="n">
-        <v>0.001</v>
+        <v>0.01</v>
       </c>
       <c r="I319" s="34" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
       </c>
       <c r="D320" s="33" t="inlineStr">
         <is>
-          <t>Клапан выпускной 602-062-001</t>
+          <t>Клапан выпускной 602-062-001-01</t>
         </is>
       </c>
       <c r="E320" s="34" t="n">
@@ -13198,7 +13198,7 @@
       </c>
       <c r="D321" s="33" t="inlineStr">
         <is>
-          <t>Клапан выпускной 602-062-001-01</t>
+          <t>Клапан пусковой главный</t>
         </is>
       </c>
       <c r="E321" s="34" t="n">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="D322" s="33" t="inlineStr">
         <is>
-          <t>Клапан пусковой главный</t>
+          <t>Опора турбины в сборе</t>
         </is>
       </c>
       <c r="E322" s="34" t="n">
@@ -13272,7 +13272,7 @@
       </c>
       <c r="D323" s="33" t="inlineStr">
         <is>
-          <t>Опора турбины в сборе</t>
+          <t>Подшипник на турбину (к-т 2шт)</t>
         </is>
       </c>
       <c r="E323" s="34" t="n">
@@ -13309,20 +13309,20 @@
       </c>
       <c r="D324" s="33" t="inlineStr">
         <is>
-          <t>Подшипник на турбину (к-т 2шт)</t>
+          <t>Штанга</t>
         </is>
       </c>
       <c r="E324" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F324" s="35" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G324" s="35" t="n">
         <v>3</v>
       </c>
       <c r="H324" s="36" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I324" s="34" t="inlineStr">
         <is>
@@ -13346,20 +13346,20 @@
       </c>
       <c r="D325" s="33" t="inlineStr">
         <is>
-          <t>Штанга</t>
+          <t>Фильтр дидероновый VD26/20</t>
         </is>
       </c>
       <c r="E325" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F325" s="35" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G325" s="35" t="n">
         <v>3</v>
       </c>
       <c r="H325" s="36" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I325" s="34" t="inlineStr">
         <is>
@@ -13383,20 +13383,20 @@
       </c>
       <c r="D326" s="33" t="inlineStr">
         <is>
-          <t>Фильтр дидероновый VD26/20</t>
+          <t>Кольцо маслосъемное с пружиной VD26/20</t>
         </is>
       </c>
       <c r="E326" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F326" s="35" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G326" s="35" t="n">
         <v>3</v>
       </c>
       <c r="H326" s="36" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="I326" s="34" t="inlineStr">
         <is>
@@ -13420,20 +13420,20 @@
       </c>
       <c r="D327" s="33" t="inlineStr">
         <is>
-          <t>Кольцо маслосъемное с пружиной VD26/20</t>
+          <t>Тросик VD26/20</t>
         </is>
       </c>
       <c r="E327" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F327" s="35" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G327" s="35" t="n">
         <v>3</v>
       </c>
       <c r="H327" s="36" t="n">
-        <v>0.001</v>
+        <v>0.01</v>
       </c>
       <c r="I327" s="34" t="inlineStr">
         <is>
@@ -13457,20 +13457,20 @@
       </c>
       <c r="D328" s="33" t="inlineStr">
         <is>
-          <t>Тросик VD26/20</t>
+          <t>Направляющая VD26/20</t>
         </is>
       </c>
       <c r="E328" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F328" s="35" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G328" s="35" t="n">
         <v>3</v>
       </c>
       <c r="H328" s="36" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I328" s="34" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="D329" s="33" t="inlineStr">
         <is>
-          <t>Направляющая VD26/20</t>
+          <t>Вкладыш мотылевый (пара)</t>
         </is>
       </c>
       <c r="E329" s="34" t="n">
@@ -13507,7 +13507,7 @@
         <v>3</v>
       </c>
       <c r="H329" s="36" t="n">
-        <v>0.02</v>
+        <v>0.001</v>
       </c>
       <c r="I329" s="34" t="inlineStr">
         <is>
@@ -13526,29 +13526,29 @@
       </c>
       <c r="C330" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D330" s="33" t="inlineStr">
         <is>
-          <t>Вкладыш мотылевый (пара)</t>
+          <t>Клапан педальный Ду25</t>
         </is>
       </c>
       <c r="E330" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F330" s="35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G330" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="F330" s="35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G330" s="35" t="n">
-        <v>3</v>
-      </c>
       <c r="H330" s="36" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="I330" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -13568,7 +13568,7 @@
       </c>
       <c r="D331" s="33" t="inlineStr">
         <is>
-          <t>Клапан педальный Ду25</t>
+          <t>Клапан штуцерный угловой Ду25</t>
         </is>
       </c>
       <c r="E331" s="34" t="n">
@@ -13642,7 +13642,7 @@
       </c>
       <c r="D333" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду25</t>
+          <t>Клапан штуцерный угловой Ду25 Ру100</t>
         </is>
       </c>
       <c r="E333" s="34" t="n">
@@ -13659,7 +13659,7 @@
       </c>
       <c r="I333" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -13679,20 +13679,20 @@
       </c>
       <c r="D334" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду25 Ру100</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру 40</t>
         </is>
       </c>
       <c r="E334" s="34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F334" s="35" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="G334" s="35" t="n">
         <v>2</v>
       </c>
       <c r="H334" s="36" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="I334" s="34" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
       </c>
       <c r="D335" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 10</t>
         </is>
       </c>
       <c r="E335" s="34" t="n">
@@ -13753,24 +13753,24 @@
       </c>
       <c r="D336" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10</t>
+          <t>Клапан дроссельный угловой штуцерный</t>
         </is>
       </c>
       <c r="E336" s="34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F336" s="35" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="G336" s="35" t="n">
         <v>2</v>
       </c>
       <c r="H336" s="36" t="n">
-        <v>0.004</v>
+        <v>0.01</v>
       </c>
       <c r="I336" s="34" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="D337" s="33" t="inlineStr">
         <is>
-          <t>Клапан дроссельный угловой штуцерный</t>
+          <t>Клапан штуцерный угловой Ду НЕРЖ</t>
         </is>
       </c>
       <c r="E337" s="34" t="n">
@@ -13822,12 +13822,12 @@
       </c>
       <c r="C338" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
         </is>
       </c>
       <c r="D338" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду НЕРЖ</t>
+          <t>Гайка Шторца рукавная Ду80Ру10</t>
         </is>
       </c>
       <c r="E338" s="34" t="n">
@@ -13844,7 +13844,7 @@
       </c>
       <c r="I338" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -13859,29 +13859,29 @@
       </c>
       <c r="C339" s="34" t="inlineStr">
         <is>
-          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D339" s="33" t="inlineStr">
         <is>
-          <t>Гайка Шторца рукавная Ду80Ру10</t>
+          <t>Клапан штуцерный проходной Ду 15 Ру 40</t>
         </is>
       </c>
       <c r="E339" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F339" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G339" s="35" t="n">
         <v>2</v>
       </c>
       <c r="H339" s="36" t="n">
-        <v>0.01</v>
+        <v>0.003</v>
       </c>
       <c r="I339" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -13901,7 +13901,7 @@
       </c>
       <c r="D340" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 15 Ру 100</t>
         </is>
       </c>
       <c r="E340" s="34" t="n">
@@ -13938,7 +13938,7 @@
       </c>
       <c r="D341" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15 Ру 100</t>
+          <t>Клапан штуцерный угловой Ду15Ру40</t>
         </is>
       </c>
       <c r="E341" s="34" t="n">
@@ -13975,7 +13975,7 @@
       </c>
       <c r="D342" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15Ру40</t>
+          <t>Клапан штуцерный угловой Ду15 Ру100</t>
         </is>
       </c>
       <c r="E342" s="34" t="n">
@@ -14007,29 +14007,29 @@
       </c>
       <c r="C343" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Запчасти к двигателям</t>
         </is>
       </c>
       <c r="D343" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15 Ру100</t>
+          <t>Кольцо уплотнительное 29,0х3,0</t>
         </is>
       </c>
       <c r="E343" s="34" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F343" s="35" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G343" s="35" t="n">
         <v>2</v>
       </c>
       <c r="H343" s="36" t="n">
-        <v>0.003</v>
+        <v>0.01</v>
       </c>
       <c r="I343" s="34" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -14044,29 +14044,29 @@
       </c>
       <c r="C344" s="34" t="inlineStr">
         <is>
-          <t>Запчасти к двигателям</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D344" s="33" t="inlineStr">
         <is>
-          <t>Кольцо уплотнительное 29,0х3,0</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
         </is>
       </c>
       <c r="E344" s="34" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F344" s="35" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="G344" s="35" t="n">
         <v>2</v>
       </c>
       <c r="H344" s="36" t="n">
-        <v>0.01</v>
+        <v>0.003</v>
       </c>
       <c r="I344" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -14118,29 +14118,29 @@
       </c>
       <c r="C346" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
         </is>
       </c>
       <c r="D346" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
+          <t>Колонка указательная с плоским рифленым стеклом Ду10Ру10</t>
         </is>
       </c>
       <c r="E346" s="34" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F346" s="35" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="G346" s="35" t="n">
         <v>2</v>
       </c>
       <c r="H346" s="36" t="n">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="I346" s="34" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -14155,29 +14155,29 @@
       </c>
       <c r="C347" s="34" t="inlineStr">
         <is>
-          <t>Головки, фланцы, гайки и стволы пожарные, стаканы</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D347" s="33" t="inlineStr">
         <is>
-          <t>Колонка указательная с плоским рифленым стеклом Ду10Ру10</t>
+          <t>Клапан невозвратный штуцерный проходной Ду20 Ру40</t>
         </is>
       </c>
       <c r="E347" s="34" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F347" s="35" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="G347" s="35" t="n">
         <v>2</v>
       </c>
       <c r="H347" s="36" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="I347" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -14197,7 +14197,7 @@
       </c>
       <c r="D348" s="33" t="inlineStr">
         <is>
-          <t>Клапан невозвратный штуцерный проходной Ду20 Ру40</t>
+          <t>Клапан невозвратный штуцерный проходной Ду20Ру160</t>
         </is>
       </c>
       <c r="E348" s="34" t="n">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="D349" s="33" t="inlineStr">
         <is>
-          <t>Клапан невозвратный штуцерный проходной Ду20Ру160</t>
+          <t>Клапан штуцерный угловой Ду20 Ру160</t>
         </is>
       </c>
       <c r="E349" s="34" t="n">
@@ -14271,7 +14271,7 @@
       </c>
       <c r="D350" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду20 Ру160</t>
+          <t>Клапан муфтовый проходной запорный Ду20Ру16</t>
         </is>
       </c>
       <c r="E350" s="34" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="D351" s="33" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду20Ру16</t>
+          <t>Сетка на фильтр Ду20 маленькая</t>
         </is>
       </c>
       <c r="E351" s="34" t="n">
@@ -24959,29 +24959,29 @@
       </c>
       <c r="C639" s="34" t="inlineStr">
         <is>
-          <t>Сепараторы и компрессоры</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D639" s="33" t="inlineStr">
         <is>
-          <t>Блокформы LBH немец.круглые (отверстие посредине)</t>
+          <t>Фильтр забортной воды Ду200 Большой</t>
         </is>
       </c>
       <c r="E639" s="34" t="n">
-        <v>71</v>
+        <v>8</v>
       </c>
       <c r="F639" s="35" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="G639" s="35" t="n">
-        <v>852</v>
+        <v>960</v>
       </c>
       <c r="H639" s="36" t="n">
-        <v>0.71</v>
+        <v>1.28</v>
       </c>
       <c r="I639" s="34" t="inlineStr">
         <is>
-          <t>ЗИП и насосы</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -24996,25 +24996,25 @@
       </c>
       <c r="C640" s="34" t="inlineStr">
         <is>
-          <t>Брашпили, лебедки, трал, подруливающие</t>
+          <t>Сепараторы и компрессоры</t>
         </is>
       </c>
       <c r="D640" s="33" t="inlineStr">
         <is>
-          <t>Кран-балка</t>
+          <t>Блокформы LBH немец.круглые (отверстие посредине)</t>
         </is>
       </c>
       <c r="E640" s="34" t="n">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="F640" s="35" t="n">
-        <v>800</v>
+        <v>12</v>
       </c>
       <c r="G640" s="35" t="n">
-        <v>800</v>
+        <v>852</v>
       </c>
       <c r="H640" s="36" t="n">
-        <v>4</v>
+        <v>0.71</v>
       </c>
       <c r="I640" s="34" t="inlineStr">
         <is>
@@ -25033,12 +25033,12 @@
       </c>
       <c r="C641" s="34" t="inlineStr">
         <is>
-          <t>Сепараторы и компрессоры</t>
+          <t>Брашпили, лебедки, трал, подруливающие</t>
         </is>
       </c>
       <c r="D641" s="33" t="inlineStr">
         <is>
-          <t>Блок цилиндров NVD48A2U</t>
+          <t>Кран-балка</t>
         </is>
       </c>
       <c r="E641" s="34" t="n">
@@ -25051,7 +25051,7 @@
         <v>800</v>
       </c>
       <c r="H641" s="36" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="I641" s="34" t="inlineStr">
         <is>
@@ -25070,29 +25070,29 @@
       </c>
       <c r="C642" s="34" t="inlineStr">
         <is>
-          <t>Насосы</t>
+          <t>Сепараторы и компрессоры</t>
         </is>
       </c>
       <c r="D642" s="33" t="inlineStr">
         <is>
-          <t>НЦВС 40/20</t>
+          <t>Блок цилиндров NVD48A2U</t>
         </is>
       </c>
       <c r="E642" s="34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F642" s="35" t="n">
-        <v>250</v>
+        <v>800</v>
       </c>
       <c r="G642" s="35" t="n">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="H642" s="36" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="I642" s="34" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>ЗИП и насосы</t>
         </is>
       </c>
     </row>
@@ -25107,29 +25107,29 @@
       </c>
       <c r="C643" s="34" t="inlineStr">
         <is>
-          <t>Сепараторы и компрессоры</t>
+          <t>Насосы</t>
         </is>
       </c>
       <c r="D643" s="33" t="inlineStr">
         <is>
-          <t>Компрессор 2ОК1 синий</t>
+          <t>НЦВС 40/20</t>
         </is>
       </c>
       <c r="E643" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F643" s="35" t="n">
-        <v>700</v>
+        <v>250</v>
       </c>
       <c r="G643" s="35" t="n">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="H643" s="36" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="I643" s="34" t="inlineStr">
         <is>
-          <t>Гараж 2</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -25166,7 +25166,7 @@
       </c>
       <c r="I644" s="34" t="inlineStr">
         <is>
-          <t>ЗИП и насосы</t>
+          <t>Гараж 2</t>
         </is>
       </c>
     </row>
@@ -25181,29 +25181,29 @@
       </c>
       <c r="C645" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Сепараторы и компрессоры</t>
         </is>
       </c>
       <c r="D645" s="33" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапановая фланцевая Ду80</t>
+          <t>Компрессор 2ОК1 синий</t>
         </is>
       </c>
       <c r="E645" s="34" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F645" s="35" t="n">
-        <v>45</v>
+        <v>700</v>
       </c>
       <c r="G645" s="35" t="n">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="H645" s="36" t="n">
-        <v>0.45</v>
+        <v>2</v>
       </c>
       <c r="I645" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>ЗИП и насосы</t>
         </is>
       </c>
     </row>
@@ -25223,24 +25223,24 @@
       </c>
       <c r="D646" s="33" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная стальная Ду300</t>
+          <t>Коробка 2-х клапановая фланцевая Ду80</t>
         </is>
       </c>
       <c r="E646" s="34" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F646" s="35" t="n">
-        <v>300</v>
+        <v>45</v>
       </c>
       <c r="G646" s="35" t="n">
-        <v>600</v>
+        <v>675</v>
       </c>
       <c r="H646" s="36" t="n">
-        <v>0.7</v>
+        <v>0.45</v>
       </c>
       <c r="I646" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -25255,25 +25255,25 @@
       </c>
       <c r="C647" s="34" t="inlineStr">
         <is>
-          <t>Сепараторы и компрессоры</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D647" s="33" t="inlineStr">
         <is>
-          <t>Барабан СЦ-1,5 (новые)</t>
+          <t>Задвижка клинкетная стальная Ду300</t>
         </is>
       </c>
       <c r="E647" s="34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F647" s="35" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="G647" s="35" t="n">
         <v>600</v>
       </c>
       <c r="H647" s="36" t="n">
-        <v>0.05</v>
+        <v>0.7</v>
       </c>
       <c r="I647" s="34" t="inlineStr">
         <is>
@@ -25297,24 +25297,24 @@
       </c>
       <c r="D648" s="33" t="inlineStr">
         <is>
-          <t>Сепаратор СЦ-1,5 с двигателем б/у</t>
+          <t>Барабан СЦ-1,5 (новые)</t>
         </is>
       </c>
       <c r="E648" s="34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F648" s="35" t="n">
-        <v>600</v>
+        <v>120</v>
       </c>
       <c r="G648" s="35" t="n">
         <v>600</v>
       </c>
       <c r="H648" s="36" t="n">
-        <v>2</v>
+        <v>0.05</v>
       </c>
       <c r="I648" s="34" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -25334,7 +25334,7 @@
       </c>
       <c r="D649" s="33" t="inlineStr">
         <is>
-          <t>Сепаратор СЦ -3 с двигателем б/у</t>
+          <t>Сепаратор СЦ-1,5 с двигателем б/у</t>
         </is>
       </c>
       <c r="E649" s="34" t="n">
@@ -25371,7 +25371,7 @@
       </c>
       <c r="D650" s="33" t="inlineStr">
         <is>
-          <t>Сепаратор СЦ-3 в разборе (без станины) б/у</t>
+          <t>Сепаратор СЦ -3 с двигателем б/у</t>
         </is>
       </c>
       <c r="E650" s="34" t="n">
@@ -25408,7 +25408,7 @@
       </c>
       <c r="D651" s="33" t="inlineStr">
         <is>
-          <t>Сепаратор СЦ-3</t>
+          <t>Сепаратор СЦ-3 в разборе (без станины) б/у</t>
         </is>
       </c>
       <c r="E651" s="34" t="n">
@@ -25425,7 +25425,7 @@
       </c>
       <c r="I651" s="34" t="inlineStr">
         <is>
-          <t>ЗИП и насосы</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -25445,7 +25445,7 @@
       </c>
       <c r="D652" s="33" t="inlineStr">
         <is>
-          <t>Сепаратор СЦ-3 ( не комплект)</t>
+          <t>Сепаратор СЦ-3</t>
         </is>
       </c>
       <c r="E652" s="34" t="n">
@@ -25482,7 +25482,7 @@
       </c>
       <c r="D653" s="33" t="inlineStr">
         <is>
-          <t>Сепаратор СЦ -1,5</t>
+          <t>Сепаратор СЦ-3 ( не комплект)</t>
         </is>
       </c>
       <c r="E653" s="34" t="n">
@@ -25514,12 +25514,12 @@
       </c>
       <c r="C654" s="34" t="inlineStr">
         <is>
-          <t>Брашпили, лебедки, трал, подруливающие</t>
+          <t>Сепараторы и компрессоры</t>
         </is>
       </c>
       <c r="D654" s="33" t="inlineStr">
         <is>
-          <t>Трал ЛЭТРС -2</t>
+          <t>Сепаратор СЦ -1,5</t>
         </is>
       </c>
       <c r="E654" s="34" t="n">
@@ -25551,29 +25551,29 @@
       </c>
       <c r="C655" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Брашпили, лебедки, трал, подруливающие</t>
         </is>
       </c>
       <c r="D655" s="33" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапановая фланцевая Ду80</t>
+          <t>Трал ЛЭТРС -2</t>
         </is>
       </c>
       <c r="E655" s="34" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F655" s="35" t="n">
-        <v>45</v>
+        <v>600</v>
       </c>
       <c r="G655" s="35" t="n">
-        <v>585</v>
+        <v>600</v>
       </c>
       <c r="H655" s="36" t="n">
-        <v>0.39</v>
+        <v>2</v>
       </c>
       <c r="I655" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>ЗИП и насосы</t>
         </is>
       </c>
     </row>
@@ -25588,29 +25588,29 @@
       </c>
       <c r="C656" s="34" t="inlineStr">
         <is>
-          <t>Сепараторы и компрессоры</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D656" s="33" t="inlineStr">
         <is>
-          <t>Блокформы LBH русск.овальные</t>
+          <t>Коробка 2-х клапановая фланцевая Ду80</t>
         </is>
       </c>
       <c r="E656" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="F656" s="35" t="n">
         <v>45</v>
       </c>
-      <c r="F656" s="35" t="n">
-        <v>12</v>
-      </c>
       <c r="G656" s="35" t="n">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="H656" s="36" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="I656" s="34" t="inlineStr">
         <is>
-          <t>ЗИП и насосы</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -25625,29 +25625,29 @@
       </c>
       <c r="C657" s="34" t="inlineStr">
         <is>
-          <t>Насосы</t>
+          <t>Сепараторы и компрессоры</t>
         </is>
       </c>
       <c r="D657" s="33" t="inlineStr">
         <is>
-          <t>Насос</t>
+          <t>Блокформы LBH русск.овальные</t>
         </is>
       </c>
       <c r="E657" s="34" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="F657" s="35" t="n">
-        <v>250</v>
+        <v>12</v>
       </c>
       <c r="G657" s="35" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="H657" s="36" t="n">
-        <v>1.6</v>
+        <v>0.45</v>
       </c>
       <c r="I657" s="34" t="inlineStr">
         <is>
-          <t>Гараж 2</t>
+          <t>ЗИП и насосы</t>
         </is>
       </c>
     </row>
@@ -25667,7 +25667,7 @@
       </c>
       <c r="D658" s="33" t="inlineStr">
         <is>
-          <t>НЦВ 100/20 двиг. 2ДМШН 160МА2 11кВт 2880об/м</t>
+          <t>Насос</t>
         </is>
       </c>
       <c r="E658" s="34" t="n">
@@ -25684,7 +25684,7 @@
       </c>
       <c r="I658" s="34" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Гараж 2</t>
         </is>
       </c>
     </row>
@@ -25699,12 +25699,12 @@
       </c>
       <c r="C659" s="34" t="inlineStr">
         <is>
-          <t>Сепараторы и компрессоры</t>
+          <t>Насосы</t>
         </is>
       </c>
       <c r="D659" s="33" t="inlineStr">
         <is>
-          <t>Насос НЦВ40/65, кап ремонт</t>
+          <t>НЦВ 100/20 двиг. 2ДМШН 160МА2 11кВт 2880об/м</t>
         </is>
       </c>
       <c r="E659" s="34" t="n">
@@ -25721,7 +25721,7 @@
       </c>
       <c r="I659" s="34" t="inlineStr">
         <is>
-          <t>ЗИП и насосы</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -25741,7 +25741,7 @@
       </c>
       <c r="D660" s="33" t="inlineStr">
         <is>
-          <t>Насос ЭВН 5/5</t>
+          <t>Насос НЦВ40/65, кап ремонт</t>
         </is>
       </c>
       <c r="E660" s="34" t="n">
@@ -25778,20 +25778,20 @@
       </c>
       <c r="D661" s="33" t="inlineStr">
         <is>
-          <t>Коленвал 18/22</t>
+          <t>Насос ЭВН 5/5</t>
         </is>
       </c>
       <c r="E661" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F661" s="35" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="G661" s="35" t="n">
         <v>500</v>
       </c>
       <c r="H661" s="36" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="I661" s="34" t="inlineStr">
         <is>
@@ -25815,20 +25815,20 @@
       </c>
       <c r="D662" s="33" t="inlineStr">
         <is>
-          <t>Насос</t>
+          <t>Коленвал 18/22</t>
         </is>
       </c>
       <c r="E662" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F662" s="35" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="G662" s="35" t="n">
         <v>500</v>
       </c>
       <c r="H662" s="36" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="I662" s="34" t="inlineStr">
         <is>
@@ -25847,29 +25847,29 @@
       </c>
       <c r="C663" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Сепараторы и компрессоры</t>
         </is>
       </c>
       <c r="D663" s="33" t="inlineStr">
         <is>
-          <t>Блины к клинкету Ду100</t>
+          <t>Насос</t>
         </is>
       </c>
       <c r="E663" s="34" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F663" s="35" t="n">
-        <v>45</v>
+        <v>250</v>
       </c>
       <c r="G663" s="35" t="n">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="H663" s="36" t="n">
-        <v>0.495</v>
+        <v>1.6</v>
       </c>
       <c r="I663" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>ЗИП и насосы</t>
         </is>
       </c>
     </row>
@@ -25884,29 +25884,29 @@
       </c>
       <c r="C664" s="34" t="inlineStr">
         <is>
-          <t>Камбузное оборудование</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D664" s="33" t="inlineStr">
         <is>
-          <t>Плита камбузная ПКЭ-300-ОМ4 3-220V; 25,2kw ;№672; 460кг; 11/91г</t>
+          <t>Блины к клинкету Ду100</t>
         </is>
       </c>
       <c r="E664" s="34" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F664" s="35" t="n">
-        <v>460</v>
+        <v>45</v>
       </c>
       <c r="G664" s="35" t="n">
-        <v>460</v>
+        <v>495</v>
       </c>
       <c r="H664" s="36" t="n">
-        <v>1.2</v>
+        <v>0.495</v>
       </c>
       <c r="I664" s="34" t="inlineStr">
         <is>
-          <t>Гараж 2</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -25926,7 +25926,7 @@
       </c>
       <c r="D665" s="33" t="inlineStr">
         <is>
-          <t>Плита камбузная ПКЭ-300-ОМ4 3-127V; 25,2kw ;№1108; 460кг; 04/92г</t>
+          <t>Плита камбузная ПКЭ-300-ОМ4 3-220V; 25,2kw ;№672; 460кг; 11/91г</t>
         </is>
       </c>
       <c r="E665" s="34" t="n">
@@ -25963,7 +25963,7 @@
       </c>
       <c r="D666" s="33" t="inlineStr">
         <is>
-          <t>Плита камбузная ПКЭ-50 (разобранная) мастерская б/у</t>
+          <t>Плита камбузная ПКЭ-300-ОМ4 3-127V; 25,2kw ;№1108; 460кг; 04/92г</t>
         </is>
       </c>
       <c r="E666" s="34" t="n">
@@ -25980,7 +25980,7 @@
       </c>
       <c r="I666" s="34" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Гараж 2</t>
         </is>
       </c>
     </row>
@@ -26000,7 +26000,7 @@
       </c>
       <c r="D667" s="33" t="inlineStr">
         <is>
-          <t>Плита камбузная ПКЭ-50 +щит+ограничитель (мастерская) б/у</t>
+          <t>Плита камбузная ПКЭ-50 (разобранная) мастерская б/у</t>
         </is>
       </c>
       <c r="E667" s="34" t="n">
@@ -26037,7 +26037,7 @@
       </c>
       <c r="D668" s="33" t="inlineStr">
         <is>
-          <t>Плита камбузная ПКЭ-50 б/у</t>
+          <t>Плита камбузная ПКЭ-50 +щит+ограничитель (мастерская) б/у</t>
         </is>
       </c>
       <c r="E668" s="34" t="n">
@@ -26069,25 +26069,25 @@
       </c>
       <c r="C669" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Камбузное оборудование</t>
         </is>
       </c>
       <c r="D669" s="33" t="inlineStr">
         <is>
-          <t>Клинкет Ду 250</t>
+          <t>Плита камбузная ПКЭ-50 б/у</t>
         </is>
       </c>
       <c r="E669" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F669" s="35" t="n">
-        <v>220</v>
+        <v>460</v>
       </c>
       <c r="G669" s="35" t="n">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="H669" s="36" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="I669" s="34" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
       </c>
       <c r="D670" s="33" t="inlineStr">
         <is>
-          <t>Клинкет Ду 250 не комплект</t>
+          <t>Клинкет Ду 250</t>
         </is>
       </c>
       <c r="E670" s="34" t="n">
@@ -26148,20 +26148,20 @@
       </c>
       <c r="D671" s="33" t="inlineStr">
         <is>
-          <t>Клинкет Ду 350</t>
+          <t>Клинкет Ду 250 не комплект</t>
         </is>
       </c>
       <c r="E671" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F671" s="35" t="n">
-        <v>400</v>
+        <v>220</v>
       </c>
       <c r="G671" s="35" t="n">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="H671" s="36" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="I671" s="34" t="inlineStr">
         <is>
@@ -26185,24 +26185,24 @@
       </c>
       <c r="D672" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду200</t>
+          <t>Клинкет Ду 350</t>
         </is>
       </c>
       <c r="E672" s="34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F672" s="35" t="n">
-        <v>130</v>
+        <v>400</v>
       </c>
       <c r="G672" s="35" t="n">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="H672" s="36" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="I672" s="34" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -26222,24 +26222,24 @@
       </c>
       <c r="D673" s="33" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая Ду80</t>
+          <t>Клапан фланцевый проходной Ду200</t>
         </is>
       </c>
       <c r="E673" s="34" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F673" s="35" t="n">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="G673" s="35" t="n">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="H673" s="36" t="n">
-        <v>0.24</v>
+        <v>0.48</v>
       </c>
       <c r="I673" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -26254,29 +26254,29 @@
       </c>
       <c r="C674" s="34" t="inlineStr">
         <is>
-          <t>Сепараторы и компрессоры</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D674" s="33" t="inlineStr">
         <is>
-          <t>Барабан СЦ-1,5 б/у КОРПУС БАРАБАНА</t>
+          <t>Фильтр заборной воды ДУ 150</t>
         </is>
       </c>
       <c r="E674" s="34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F674" s="35" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="G674" s="35" t="n">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="H674" s="36" t="n">
-        <v>0.03</v>
+        <v>0.5</v>
       </c>
       <c r="I674" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -26296,24 +26296,24 @@
       </c>
       <c r="D675" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду125</t>
+          <t>Коробка 3-х клап.фланцевая Ду80</t>
         </is>
       </c>
       <c r="E675" s="34" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F675" s="35" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G675" s="35" t="n">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="H675" s="36" t="n">
-        <v>0.42</v>
+        <v>0.24</v>
       </c>
       <c r="I675" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -26328,29 +26328,29 @@
       </c>
       <c r="C676" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Сепараторы и компрессоры</t>
         </is>
       </c>
       <c r="D676" s="33" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду100</t>
+          <t>Барабан СЦ-1,5 б/у КОРПУС БАРАБАНА</t>
         </is>
       </c>
       <c r="E676" s="34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F676" s="35" t="n">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="G676" s="35" t="n">
-        <v>270</v>
+        <v>360</v>
       </c>
       <c r="H676" s="36" t="n">
-        <v>0.27</v>
+        <v>0.03</v>
       </c>
       <c r="I676" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -26370,20 +26370,20 @@
       </c>
       <c r="D677" s="33" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая невозврат.Ду80 Ру6</t>
+          <t>Клапан фланцевый проходной Ду125</t>
         </is>
       </c>
       <c r="E677" s="34" t="n">
         <v>6</v>
       </c>
       <c r="F677" s="35" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G677" s="35" t="n">
-        <v>270</v>
+        <v>330</v>
       </c>
       <c r="H677" s="36" t="n">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="I677" s="34" t="inlineStr">
         <is>
@@ -26402,29 +26402,29 @@
       </c>
       <c r="C678" s="34" t="inlineStr">
         <is>
-          <t>Насосы</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D678" s="33" t="inlineStr">
         <is>
-          <t>Насос НЦВ 100/80</t>
+          <t>Задвижка клинкетная Ду100</t>
         </is>
       </c>
       <c r="E678" s="34" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F678" s="35" t="n">
-        <v>250</v>
+        <v>45</v>
       </c>
       <c r="G678" s="35" t="n">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="H678" s="36" t="n">
-        <v>0.8</v>
+        <v>0.27</v>
       </c>
       <c r="I678" s="34" t="inlineStr">
         <is>
-          <t>Гараж 1</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -26439,29 +26439,29 @@
       </c>
       <c r="C679" s="34" t="inlineStr">
         <is>
-          <t>Насосы</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D679" s="33" t="inlineStr">
         <is>
-          <t>Насос ЭСН-11А пост. 175/320В, 9,6/19,5кВт, 2400/3750 об/м</t>
+          <t>Коробка 3-х клап.фланцевая невозврат.Ду80 Ру6</t>
         </is>
       </c>
       <c r="E679" s="34" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F679" s="35" t="n">
-        <v>250</v>
+        <v>45</v>
       </c>
       <c r="G679" s="35" t="n">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="H679" s="36" t="n">
-        <v>0.8</v>
+        <v>0.18</v>
       </c>
       <c r="I679" s="34" t="inlineStr">
         <is>
-          <t>Гараж 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -26481,7 +26481,7 @@
       </c>
       <c r="D680" s="33" t="inlineStr">
         <is>
-          <t>Насос НЦВ 40/20 ?</t>
+          <t>Насос НЦВ 100/80</t>
         </is>
       </c>
       <c r="E680" s="34" t="n">
@@ -26498,7 +26498,7 @@
       </c>
       <c r="I680" s="34" t="inlineStr">
         <is>
-          <t>Контейнер 1</t>
+          <t>Гараж 1</t>
         </is>
       </c>
     </row>
@@ -26518,7 +26518,7 @@
       </c>
       <c r="D681" s="33" t="inlineStr">
         <is>
-          <t>Насос НЦВС 63/30 новый</t>
+          <t>Насос ЭСН-11А пост. 175/320В, 9,6/19,5кВт, 2400/3750 об/м</t>
         </is>
       </c>
       <c r="E681" s="34" t="n">
@@ -26535,7 +26535,7 @@
       </c>
       <c r="I681" s="34" t="inlineStr">
         <is>
-          <t>Контейнер 2</t>
+          <t>Гараж 2</t>
         </is>
       </c>
     </row>
@@ -26555,7 +26555,7 @@
       </c>
       <c r="D682" s="33" t="inlineStr">
         <is>
-          <t>Насос пресновод.д/осушения танков 4390/4-588-001</t>
+          <t>Насос НЦВ 40/20 ?</t>
         </is>
       </c>
       <c r="E682" s="34" t="n">
@@ -26572,7 +26572,7 @@
       </c>
       <c r="I682" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Контейнер 1</t>
         </is>
       </c>
     </row>
@@ -26592,7 +26592,7 @@
       </c>
       <c r="D683" s="33" t="inlineStr">
         <is>
-          <t>Насос ЭВН 5/5</t>
+          <t>Насос НЦВС 63/30 новый</t>
         </is>
       </c>
       <c r="E683" s="34" t="n">
@@ -26609,7 +26609,7 @@
       </c>
       <c r="I683" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Контейнер 2</t>
         </is>
       </c>
     </row>
@@ -26629,7 +26629,7 @@
       </c>
       <c r="D684" s="33" t="inlineStr">
         <is>
-          <t>Насос НЦВ 63/20 с двигателем 14кВт</t>
+          <t>Насос пресновод.д/осушения танков 4390/4-588-001</t>
         </is>
       </c>
       <c r="E684" s="34" t="n">
@@ -26646,7 +26646,7 @@
       </c>
       <c r="I684" s="34" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -26666,7 +26666,7 @@
       </c>
       <c r="D685" s="33" t="inlineStr">
         <is>
-          <t>Насос НЦВС 63/20 с трубками</t>
+          <t>Насос ЭВН 5/5</t>
         </is>
       </c>
       <c r="E685" s="34" t="n">
@@ -26683,7 +26683,7 @@
       </c>
       <c r="I685" s="34" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -26703,7 +26703,7 @@
       </c>
       <c r="D686" s="33" t="inlineStr">
         <is>
-          <t>НЦВ 63/20 или НЦВ 40/30 двиг. АМ52-2 8кВт 2850об/м</t>
+          <t>Насос НЦВ 63/20 с двигателем 14кВт</t>
         </is>
       </c>
       <c r="E686" s="34" t="n">
@@ -26740,7 +26740,7 @@
       </c>
       <c r="D687" s="33" t="inlineStr">
         <is>
-          <t>НЦВ 63/20 двиг. ДМ32В2 7,5кВт 2900об/м</t>
+          <t>Насос НЦВС 63/20 с трубками</t>
         </is>
       </c>
       <c r="E687" s="34" t="n">
@@ -26777,7 +26777,7 @@
       </c>
       <c r="D688" s="33" t="inlineStr">
         <is>
-          <t>НЦВ 25/80 или НЦВС 40/65 двиг.АМ62-2 14кВт 2850об/м</t>
+          <t>НЦВ 63/20 или НЦВ 40/30 двиг. АМ52-2 8кВт 2850об/м</t>
         </is>
       </c>
       <c r="E688" s="34" t="n">
@@ -26814,7 +26814,7 @@
       </c>
       <c r="D689" s="33" t="inlineStr">
         <is>
-          <t>НЦВ 40/80 двиг.АМ70-2 19кВт 2900об/м</t>
+          <t>НЦВ 63/20 двиг. ДМ32В2 7,5кВт 2900об/м</t>
         </is>
       </c>
       <c r="E689" s="34" t="n">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="C690" s="34" t="inlineStr">
         <is>
-          <t>Сепараторы и компрессоры</t>
+          <t>Насосы</t>
         </is>
       </c>
       <c r="D690" s="33" t="inlineStr">
         <is>
-          <t>Насос НЦВП 315/10 новый</t>
+          <t>НЦВ 25/80 или НЦВС 40/65 двиг.АМ62-2 14кВт 2850об/м</t>
         </is>
       </c>
       <c r="E690" s="34" t="n">
@@ -26868,7 +26868,7 @@
       </c>
       <c r="I690" s="34" t="inlineStr">
         <is>
-          <t>ЗИП и насосы</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -26883,12 +26883,12 @@
       </c>
       <c r="C691" s="34" t="inlineStr">
         <is>
-          <t>Сепараторы и компрессоры</t>
+          <t>Насосы</t>
         </is>
       </c>
       <c r="D691" s="33" t="inlineStr">
         <is>
-          <t>Насос НЦВС 40/20, кап. ремонт</t>
+          <t>НЦВ 40/80 двиг.АМ70-2 19кВт 2900об/м</t>
         </is>
       </c>
       <c r="E691" s="34" t="n">
@@ -26905,7 +26905,7 @@
       </c>
       <c r="I691" s="34" t="inlineStr">
         <is>
-          <t>ЗИП и насосы</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -26925,7 +26925,7 @@
       </c>
       <c r="D692" s="33" t="inlineStr">
         <is>
-          <t>Насос НЦВ 40/65 б/у</t>
+          <t>Насос НЦВП 315/10 новый</t>
         </is>
       </c>
       <c r="E692" s="34" t="n">
@@ -26962,7 +26962,7 @@
       </c>
       <c r="D693" s="33" t="inlineStr">
         <is>
-          <t>Насос НЦВС 40/20 б/у</t>
+          <t>Насос НЦВС 40/20, кап. ремонт</t>
         </is>
       </c>
       <c r="E693" s="34" t="n">
@@ -26999,7 +26999,7 @@
       </c>
       <c r="D694" s="33" t="inlineStr">
         <is>
-          <t>Насос ЭСН-11А пост. 175/320В, 9,6/19,5кВт, 2400/3750 об/м</t>
+          <t>Насос НЦВ 40/65 б/у</t>
         </is>
       </c>
       <c r="E694" s="34" t="n">
@@ -27036,24 +27036,24 @@
       </c>
       <c r="D695" s="33" t="inlineStr">
         <is>
-          <t>Барабан СЦ-3 б/у КОРПУС БАРАБАНА</t>
+          <t>Насос НЦВС 40/20 б/у</t>
         </is>
       </c>
       <c r="E695" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F695" s="35" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="G695" s="35" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="H695" s="36" t="n">
-        <v>0.02</v>
+        <v>0.8</v>
       </c>
       <c r="I695" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>ЗИП и насосы</t>
         </is>
       </c>
     </row>
@@ -27073,20 +27073,20 @@
       </c>
       <c r="D696" s="33" t="inlineStr">
         <is>
-          <t>Ротор</t>
+          <t>Насос ЭСН-11А пост. 175/320В, 9,6/19,5кВт, 2400/3750 об/м</t>
         </is>
       </c>
       <c r="E696" s="34" t="n">
         <v>1</v>
       </c>
       <c r="F696" s="35" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="G696" s="35" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H696" s="36" t="n">
-        <v>0.01</v>
+        <v>0.8</v>
       </c>
       <c r="I696" s="34" t="inlineStr">
         <is>
@@ -27105,29 +27105,29 @@
       </c>
       <c r="C697" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Сепараторы и компрессоры</t>
         </is>
       </c>
       <c r="D697" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду125 Ру10</t>
+          <t>Барабан СЦ-3 б/у КОРПУС БАРАБАНА</t>
         </is>
       </c>
       <c r="E697" s="34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F697" s="35" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="G697" s="35" t="n">
-        <v>165</v>
+        <v>240</v>
       </c>
       <c r="H697" s="36" t="n">
-        <v>0.21</v>
+        <v>0.02</v>
       </c>
       <c r="I697" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -27147,24 +27147,24 @@
       </c>
       <c r="D698" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду150</t>
+          <t>Фильтр забортной воды Ду 300</t>
         </is>
       </c>
       <c r="E698" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F698" s="35" t="n">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="G698" s="35" t="n">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="H698" s="36" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="I698" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -27179,29 +27179,29 @@
       </c>
       <c r="C699" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Сепараторы и компрессоры</t>
         </is>
       </c>
       <c r="D699" s="33" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая Ду80</t>
+          <t>Ротор</t>
         </is>
       </c>
       <c r="E699" s="34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F699" s="35" t="n">
-        <v>45</v>
+        <v>200</v>
       </c>
       <c r="G699" s="35" t="n">
-        <v>135</v>
+        <v>200</v>
       </c>
       <c r="H699" s="36" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="I699" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>ЗИП и насосы</t>
         </is>
       </c>
     </row>
@@ -27221,20 +27221,20 @@
       </c>
       <c r="D700" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду200 Ру6</t>
+          <t>Клапан фланцевый проходной Ду125 Ру10</t>
         </is>
       </c>
       <c r="E700" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F700" s="35" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="G700" s="35" t="n">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="H700" s="36" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="I700" s="34" t="inlineStr">
         <is>
@@ -27253,29 +27253,29 @@
       </c>
       <c r="C701" s="34" t="inlineStr">
         <is>
-          <t>Сепараторы и компрессоры</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D701" s="33" t="inlineStr">
         <is>
-          <t>Барабан СЦ-1,5 б/у ( в сборе)</t>
+          <t>Клапан фланцевый проходной Ду150</t>
         </is>
       </c>
       <c r="E701" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F701" s="35" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="G701" s="35" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H701" s="36" t="n">
-        <v>0.01</v>
+        <v>0.2</v>
       </c>
       <c r="I701" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -27290,29 +27290,29 @@
       </c>
       <c r="C702" s="34" t="inlineStr">
         <is>
-          <t>Сепараторы и компрессоры</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D702" s="33" t="inlineStr">
         <is>
-          <t>Весы для ЛБАШ</t>
+          <t>Коробка 3-х клап.фланцевая Ду80</t>
         </is>
       </c>
       <c r="E702" s="34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F702" s="35" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="G702" s="35" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="H702" s="36" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="I702" s="34" t="inlineStr">
         <is>
-          <t>ЗИП и насосы</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -27332,24 +27332,24 @@
       </c>
       <c r="D703" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду125 ок.входа</t>
+          <t>Клапан фланцевый проходной Ду200 Ру6</t>
         </is>
       </c>
       <c r="E703" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F703" s="35" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="G703" s="35" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H703" s="36" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="I703" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -27364,29 +27364,29 @@
       </c>
       <c r="C704" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Сепараторы и компрессоры</t>
         </is>
       </c>
       <c r="D704" s="33" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапановая фланцевая Ду50</t>
+          <t>Барабан СЦ-1,5 б/у ( в сборе)</t>
         </is>
       </c>
       <c r="E704" s="34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F704" s="35" t="n">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="G704" s="35" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H704" s="36" t="n">
-        <v>0.048</v>
+        <v>0.01</v>
       </c>
       <c r="I704" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -27401,29 +27401,29 @@
       </c>
       <c r="C705" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Сепараторы и компрессоры</t>
         </is>
       </c>
       <c r="D705" s="33" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду 100 БРОНЗА</t>
+          <t>Весы для ЛБАШ</t>
         </is>
       </c>
       <c r="E705" s="34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F705" s="35" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="G705" s="35" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H705" s="36" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="I705" s="34" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>ЗИП и насосы</t>
         </is>
       </c>
     </row>
@@ -27443,24 +27443,24 @@
       </c>
       <c r="D706" s="33" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая невозврат.Ду80 Ру6</t>
+          <t>Клапан фланцевый проходной Ду125 ок.входа</t>
         </is>
       </c>
       <c r="E706" s="34" t="n">
         <v>2</v>
       </c>
       <c r="F706" s="35" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G706" s="35" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="H706" s="36" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="I706" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -27480,20 +27480,20 @@
       </c>
       <c r="D707" s="33" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапановая фланцевая Ду80</t>
+          <t>Коробка 2-х клапановая фланцевая Ду50</t>
         </is>
       </c>
       <c r="E707" s="34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F707" s="35" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="G707" s="35" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H707" s="36" t="n">
-        <v>0.06</v>
+        <v>0.048</v>
       </c>
       <c r="I707" s="34" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="D708" s="33" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапановая фланцевая Ду80</t>
+          <t>Задвижка клинкетная Ду 100 БРОНЗА</t>
         </is>
       </c>
       <c r="E708" s="34" t="n">
@@ -27530,11 +27530,11 @@
         <v>90</v>
       </c>
       <c r="H708" s="36" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="I708" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -27554,7 +27554,7 @@
       </c>
       <c r="D709" s="33" t="inlineStr">
         <is>
-          <t>Клинкет Ду 100, сталь</t>
+          <t>Коробка 3-х клап.фланцевая невозврат.Ду80 Ру6</t>
         </is>
       </c>
       <c r="E709" s="34" t="n">
@@ -27567,11 +27567,11 @@
         <v>90</v>
       </c>
       <c r="H709" s="36" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="I709" s="34" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -27586,29 +27586,29 @@
       </c>
       <c r="C710" s="34" t="inlineStr">
         <is>
-          <t>Сепараторы и компрессоры</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D710" s="33" t="inlineStr">
         <is>
-          <t>Кулачки СЦ-1,5</t>
+          <t>Коробка 2-х клапановая фланцевая Ду80</t>
         </is>
       </c>
       <c r="E710" s="34" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="F710" s="35" t="n">
-        <v>1.5</v>
+        <v>45</v>
       </c>
       <c r="G710" s="35" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H710" s="36" t="n">
-        <v>0.55</v>
+        <v>0.06</v>
       </c>
       <c r="I710" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -27628,24 +27628,24 @@
       </c>
       <c r="D711" s="33" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая Ду50</t>
+          <t>Коробка 2-х клапановая фланцевая Ду80</t>
         </is>
       </c>
       <c r="E711" s="34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F711" s="35" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="G711" s="35" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="H711" s="36" t="n">
-        <v>0.036</v>
+        <v>0.06</v>
       </c>
       <c r="I711" s="34" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -27665,24 +27665,24 @@
       </c>
       <c r="D712" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду150 Ру10</t>
+          <t>Клинкет Ду 100, сталь</t>
         </is>
       </c>
       <c r="E712" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F712" s="35" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="G712" s="35" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="H712" s="36" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I712" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -27697,29 +27697,29 @@
       </c>
       <c r="C713" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Сепараторы и компрессоры</t>
         </is>
       </c>
       <c r="D713" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду150 Ру10</t>
+          <t>Кулачки СЦ-1,5</t>
         </is>
       </c>
       <c r="E713" s="34" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="F713" s="35" t="n">
-        <v>75</v>
+        <v>1.5</v>
       </c>
       <c r="G713" s="35" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H713" s="36" t="n">
-        <v>0.1</v>
+        <v>0.55</v>
       </c>
       <c r="I713" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -27739,20 +27739,20 @@
       </c>
       <c r="D714" s="33" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая Ду100</t>
+          <t>Коробка 3-х клап.фланцевая Ду50</t>
         </is>
       </c>
       <c r="E714" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F714" s="35" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="G714" s="35" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H714" s="36" t="n">
-        <v>0.045</v>
+        <v>0.036</v>
       </c>
       <c r="I714" s="34" t="inlineStr">
         <is>
@@ -27776,24 +27776,24 @@
       </c>
       <c r="D715" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду 125 (без чертежа)</t>
+          <t>Клапан фланцевый угловой Ду150 Ру10</t>
         </is>
       </c>
       <c r="E715" s="34" t="n">
         <v>1</v>
       </c>
       <c r="F715" s="35" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="G715" s="35" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="H715" s="36" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I715" s="34" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -27808,29 +27808,29 @@
       </c>
       <c r="C716" s="34" t="inlineStr">
         <is>
-          <t>Сепараторы и компрессоры</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D716" s="33" t="inlineStr">
         <is>
-          <t>Кулачки СЦ-3</t>
+          <t>Клапан фланцевый угловой Ду150 Ру10</t>
         </is>
       </c>
       <c r="E716" s="34" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="F716" s="35" t="n">
-        <v>1.5</v>
+        <v>75</v>
       </c>
       <c r="G716" s="35" t="n">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="H716" s="36" t="n">
-        <v>0.36</v>
+        <v>0.1</v>
       </c>
       <c r="I716" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -27850,20 +27850,20 @@
       </c>
       <c r="D717" s="33" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапановая фланцевая Ду50</t>
+          <t>Коробка 3-х клап.фланцевая Ду100</t>
         </is>
       </c>
       <c r="E717" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F717" s="35" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="G717" s="35" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H717" s="36" t="n">
-        <v>0.024</v>
+        <v>0.045</v>
       </c>
       <c r="I717" s="34" t="inlineStr">
         <is>
@@ -27887,24 +27887,24 @@
       </c>
       <c r="D718" s="33" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая запорная Ду50 Ру6</t>
+          <t>Клапан фланцевый проходной Ду 125 (без чертежа)</t>
         </is>
       </c>
       <c r="E718" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F718" s="35" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G718" s="35" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H718" s="36" t="n">
-        <v>0.024</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I718" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -27919,29 +27919,29 @@
       </c>
       <c r="C719" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Сепараторы и компрессоры</t>
         </is>
       </c>
       <c r="D719" s="33" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду100 без штока и блинов ( в разборе)</t>
+          <t>Кулачки СЦ-3</t>
         </is>
       </c>
       <c r="E719" s="34" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F719" s="35" t="n">
-        <v>45</v>
+        <v>1.5</v>
       </c>
       <c r="G719" s="35" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="H719" s="36" t="n">
-        <v>0.045</v>
+        <v>0.36</v>
       </c>
       <c r="I719" s="34" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -27961,24 +27961,24 @@
       </c>
       <c r="D720" s="33" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапанная корпус</t>
+          <t>Коробка 2-х клапановая фланцевая Ду50</t>
         </is>
       </c>
       <c r="E720" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F720" s="35" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G720" s="35" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H720" s="36" t="n">
-        <v>0.01</v>
+        <v>0.024</v>
       </c>
       <c r="I720" s="34" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -27998,24 +27998,24 @@
       </c>
       <c r="D721" s="33" t="inlineStr">
         <is>
-          <t>Фильтр забортной воды Ду200 Большой</t>
+          <t>Коробка 3-х клап.фланцевая запорная Ду50 Ру6</t>
         </is>
       </c>
       <c r="E721" s="34" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F721" s="35" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G721" s="35" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H721" s="36" t="n">
-        <v>1.28</v>
+        <v>0.024</v>
       </c>
       <c r="I721" s="34" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -28030,29 +28030,29 @@
       </c>
       <c r="C722" s="34" t="inlineStr">
         <is>
-          <t>Сепараторы и компрессоры</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D722" s="33" t="inlineStr">
         <is>
-          <t>Электропривод к задвижке</t>
+          <t>Задвижка клинкетная Ду100 без штока и блинов ( в разборе)</t>
         </is>
       </c>
       <c r="E722" s="34" t="n">
         <v>1</v>
       </c>
       <c r="F722" s="35" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G722" s="35" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H722" s="36" t="n">
-        <v>0.01</v>
+        <v>0.045</v>
       </c>
       <c r="I722" s="34" t="inlineStr">
         <is>
-          <t>ЗИП и насосы</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -28067,29 +28067,29 @@
       </c>
       <c r="C723" s="34" t="inlineStr">
         <is>
-          <t>Сепараторы и компрессоры</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D723" s="33" t="inlineStr">
         <is>
-          <t>Ремкомплект СЦ-3</t>
+          <t>Коробка 2-х клапанная корпус</t>
         </is>
       </c>
       <c r="E723" s="34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F723" s="35" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="G723" s="35" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H723" s="36" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="I723" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -28104,29 +28104,29 @@
       </c>
       <c r="C724" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Сепараторы и компрессоры</t>
         </is>
       </c>
       <c r="D724" s="33" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая запорная Ду50 Ру6</t>
+          <t>Электропривод к задвижке</t>
         </is>
       </c>
       <c r="E724" s="34" t="n">
         <v>1</v>
       </c>
       <c r="F724" s="35" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="G724" s="35" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H724" s="36" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="I724" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>ЗИП и насосы</t>
         </is>
       </c>
     </row>
@@ -28141,29 +28141,29 @@
       </c>
       <c r="C725" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Сепараторы и компрессоры</t>
         </is>
       </c>
       <c r="D725" s="33" t="inlineStr">
         <is>
-          <t>Фильтр заборной воды ДУ 150</t>
+          <t>Ремкомплект СЦ-3</t>
         </is>
       </c>
       <c r="E725" s="34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F725" s="35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G725" s="35" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H725" s="36" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="I725" s="34" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -28178,29 +28178,29 @@
       </c>
       <c r="C726" s="34" t="inlineStr">
         <is>
-          <t>Сепараторы и компрессоры</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="D726" s="33" t="inlineStr">
         <is>
-          <t>Ремкомплект СЦ-1,5</t>
+          <t>Коробка 3-х клап.фланцевая запорная Ду50 Ру6</t>
         </is>
       </c>
       <c r="E726" s="34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F726" s="35" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="G726" s="35" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H726" s="36" t="n">
-        <v>0.05</v>
+        <v>0.012</v>
       </c>
       <c r="I726" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -28215,29 +28215,29 @@
       </c>
       <c r="C727" s="34" t="inlineStr">
         <is>
-          <t>Камбузное оборудование</t>
+          <t>Сепараторы и компрессоры</t>
         </is>
       </c>
       <c r="D727" s="33" t="inlineStr">
         <is>
-          <t>Вилка к ПКЭ-300</t>
+          <t>Ремкомплект СЦ-1,5</t>
         </is>
       </c>
       <c r="E727" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F727" s="35" t="n">
         <v>3</v>
       </c>
       <c r="G727" s="35" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H727" s="36" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="I727" s="34" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -28252,12 +28252,12 @@
       </c>
       <c r="C728" s="34" t="inlineStr">
         <is>
-          <t>Сепараторы и компрессоры</t>
+          <t>Камбузное оборудование</t>
         </is>
       </c>
       <c r="D728" s="33" t="inlineStr">
         <is>
-          <t>Клапан компресс. ЭКП 70/25</t>
+          <t>Вилка к ПКЭ-300</t>
         </is>
       </c>
       <c r="E728" s="34" t="n">
@@ -28289,29 +28289,29 @@
       </c>
       <c r="C729" s="34" t="inlineStr">
         <is>
-          <t>Насосы</t>
+          <t>Сепараторы и компрессоры</t>
         </is>
       </c>
       <c r="D729" s="33" t="inlineStr">
         <is>
-          <t>Крылатка на насос забортной воды</t>
+          <t>Клапан компресс. ЭКП 70/25</t>
         </is>
       </c>
       <c r="E729" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F729" s="35" t="n">
         <v>3</v>
       </c>
       <c r="G729" s="35" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H729" s="36" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="I729" s="34" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -28326,29 +28326,29 @@
       </c>
       <c r="C730" s="34" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Насосы</t>
         </is>
       </c>
       <c r="D730" s="33" t="inlineStr">
         <is>
-          <t>Клапан проходной ДУ 125 корпус</t>
+          <t>Крылатка на насос забортной воды</t>
         </is>
       </c>
       <c r="E730" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F730" s="35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G730" s="35" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H730" s="36" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="I730" s="34" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -28368,7 +28368,7 @@
       </c>
       <c r="D731" s="33" t="inlineStr">
         <is>
-          <t>Фильтр забортной воды Ду 300</t>
+          <t>Клапан проходной ДУ 125 корпус</t>
         </is>
       </c>
       <c r="E731" s="34" t="n">
@@ -28381,11 +28381,11 @@
         <v>5</v>
       </c>
       <c r="H731" s="36" t="n">
-        <v>0.35</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I731" s="34" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
